--- a/docs/xlsx/jobs-2026-08-17.xlsx
+++ b/docs/xlsx/jobs-2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="955">
   <si>
     <t>Title</t>
   </si>
@@ -577,6 +577,66 @@
     <t>https://www.conservationjobboard.com/job-listing-wind-river-karelian-bear-dog-partners-program-intern-florence-montana/3308738659</t>
   </si>
   <si>
+    <t>Conservation Specialist II</t>
+  </si>
+  <si>
+    <t>City of Chula Vista</t>
+  </si>
+  <si>
+    <t>Chula Vista, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/conservation-specialist-ii/</t>
+  </si>
+  <si>
+    <t>Senior Energy and Climate Analyst</t>
+  </si>
+  <si>
+    <t>The Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, Virginia, United States</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Clean Energy</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-energy-and-climate-analyst/</t>
+  </si>
+  <si>
+    <t>2026 BES Fellowship for Founding School Leaders - Alabama</t>
+  </si>
+  <si>
+    <t>BES</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/360eeb8be1d44f23be3bbef8818344cd-2026-bes-fellowship-for-founding-school-leaders-alabama-bes-boston</t>
+  </si>
+  <si>
     <t>2027-2029 Legal Fellowship (Voting Right Project)</t>
   </si>
   <si>
@@ -586,9 +646,6 @@
     <t>Remote</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 65000.00/year</t>
   </si>
   <si>
@@ -598,6 +655,129 @@
     <t>https://www.idealist.org/en/nonprofit-job/387a2ef4ebf647f383ded363e38f4e0a-2027-2029-legal-fellowship-voting-right-project-fair-elections-center-washington</t>
   </si>
   <si>
+    <t>Account Associate (Bilingual Spanish/ English)</t>
+  </si>
+  <si>
+    <t>All In Energy</t>
+  </si>
+  <si>
+    <t>Lawrence, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 31.16 - 31.16/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce9fb0596c424203841f7ba7e4424679-account-associate-bilingual-spanish-english-all-in-energy-lawrence</t>
+  </si>
+  <si>
+    <t>Accounting and Vendor Relations Analyst</t>
+  </si>
+  <si>
+    <t>Association for Community Affiliated Plans</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b77949e4cc2e496e9e1866c8529c446e-accounting-and-vendor-relations-analyst-association-for-community-affiliated-plans-washington</t>
+  </si>
+  <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>SCELC: Statewide California Electronic Library Consortium</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a61ee0b7fc194dae8f5fe9e53ceee9d9-accounting-manager-scelc-statewide-california-electronic-library-consortium-los-angeles</t>
+  </si>
+  <si>
+    <t>Activity Specialist – School Year 2026 - 2027</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/874e7d5ef9fa4135a401c9d0847d4c5f-activity-specialist-school-year-2026-2027-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Administration Manager</t>
+  </si>
+  <si>
+    <t>Project Equity</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/810105015167446c86dcdd1e3bdcd71d-administration-manager-project-equity-oakland</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>WV FREE</t>
+  </si>
+  <si>
+    <t>Charleston, West Virginia</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a23aa7d4407a4e28b9f645af43d5b433-administrative-coordinator-wv-free-charleston</t>
+  </si>
+  <si>
+    <t>Administrative Support Clerk</t>
+  </si>
+  <si>
+    <t>Legal Services of Northern California</t>
+  </si>
+  <si>
+    <t>Redding, California</t>
+  </si>
+  <si>
+    <t>USD 3750.00 - 5299.00/month</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/113af05dba774cd4b4ecb9d4558b6004-administrative-support-clerk-legal-services-of-northern-california-redding</t>
+  </si>
+  <si>
     <t>Adoption Counselor</t>
   </si>
   <si>
@@ -616,6 +796,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/e6417a9658104e3bbf22732929bb753d-adoption-counselor-orphans-of-the-storm-riverwoods</t>
   </si>
   <si>
+    <t>Advocacy Manager</t>
+  </si>
+  <si>
+    <t>Amargosa Conservancy</t>
+  </si>
+  <si>
+    <t>Las Vegas, Nevada</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf184e838da94842987d8ab5d37fc120-advocacy-manager-amargosa-conservancy-las-vegas</t>
+  </si>
+  <si>
+    <t>Aftercare Associate</t>
+  </si>
+  <si>
+    <t>ACE (Association of Community Employment Programs for the Homeless, Inc.)</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7bcb71c24bc46dbacd022079253cc8e-aftercare-associate-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
     <t>Agência do Bem - Oficineiro de Musicalização Infantil</t>
   </si>
   <si>
@@ -631,12 +847,126 @@
     <t>BRL 57.00 - 57.00/hour</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/6e5f7635c9ab4e0aaef26d496a3decd8-agencia-do-bem-oficineiro-de-musicalizacao-infantil-agencia-do-bem-duque-de-caxias</t>
   </si>
   <si>
+    <t>Albany Organizer</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 55300.00 - 64500.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd1727f4215d4d8086f00bc510d2afb6-albany-organizer-food-water-watch-albany</t>
+  </si>
+  <si>
+    <t>American Academy in Rome - Director</t>
+  </si>
+  <si>
+    <t>American Academy in Rome</t>
+  </si>
+  <si>
+    <t>Rome, Lazio, IT</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73659a6acb5f4e80a45ae81864d9d282-american-academy-in-rome-director-american-academy-in-rome-rome</t>
+  </si>
+  <si>
+    <t>AMGA Director of Development</t>
+  </si>
+  <si>
+    <t>American Mountain Guides Association</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57d40b82a7347dbbb40627a8521b382-amga-director-of-development-american-mountain-guides-association-boulder</t>
+  </si>
+  <si>
+    <t>Assistant Supervising Attorney</t>
+  </si>
+  <si>
+    <t>The Immigrant Law Center of Minnesota</t>
+  </si>
+  <si>
+    <t>Saint Paul, MN</t>
+  </si>
+  <si>
+    <t>USD 91984.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94d632e245514a70bc139330da7e7726-assistant-supervising-attorney-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
+    <t>Attendance Resource Coordinator</t>
+  </si>
+  <si>
+    <t>Communities In Schools of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96197c438dcf46ab81fe46c34461f860-attendance-resource-coordinator-communities-in-schools-of-the-nations-capital-washington</t>
+  </si>
+  <si>
+    <t>Attorney</t>
+  </si>
+  <si>
+    <t>Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c3d351869b0456a9d7af2c01ea85b2b-attorney-foundation-for-individual-rights-and-expression-philadelphia</t>
+  </si>
+  <si>
+    <t>Become a Campaign Organizer in Nebraska!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Scottsbluff, Nebraska</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/0b51e92ab4f0449f8dcf2480cbdbc6fa-become-a-campaign-organizer-in-nebraska-the-outreach-team-scottsbluff</t>
+  </si>
+  <si>
     <t>Bilingual Fundraising &amp; Grants Specialist</t>
   </si>
   <si>
@@ -649,6 +979,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/499014b7ad3345d3a8ecf01f2fdf8b71-bilingual-fundraising-grants-specialist-ideas-mexico-heroica-puebla-de-zaragoza</t>
   </si>
   <si>
+    <t>Breaking Barriers Collaborative - Communications Manager</t>
+  </si>
+  <si>
+    <t>Climate Solutions</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 93000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Economic Development, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5034c9bc250b4ed5bb17707165d780b8-breaking-barriers-collaborative-communications-manager-climate-solutions-seattle</t>
+  </si>
+  <si>
+    <t>Business Acquisition Lead</t>
+  </si>
+  <si>
+    <t>American Montessori Society</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/940f5d60fe4f4a8db0217a3a807d77db-business-acquisition-lead-american-montessori-society-new-york</t>
+  </si>
+  <si>
+    <t>Business and Finance Manager</t>
+  </si>
+  <si>
+    <t>Catskill Montessori School</t>
+  </si>
+  <si>
+    <t>Catskill, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c83aea2063b44ecbbf4a27eb2bad259-business-and-finance-manager-catskill-montessori-school-catskill</t>
+  </si>
+  <si>
+    <t>Case Manager (Bilingual Spanish)</t>
+  </si>
+  <si>
+    <t>Nourishing Hope</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f031351c4534092842734282f3e36b9-case-manager-bilingual-spanish-nourishing-hope-chicago</t>
+  </si>
+  <si>
     <t>Chef de Mission - Roster</t>
   </si>
   <si>
@@ -664,6 +1060,126 @@
     <t>https://www.idealist.org/en/nonprofit-job/c76a251b376e41f3af450d2f352cb937-chef-de-mission-roster-intersos-rome</t>
   </si>
   <si>
+    <t>Climate Justice Organizer</t>
+  </si>
+  <si>
+    <t>UPROSE</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d786fe65913544a8a2dca6543b9c2ee5-climate-justice-organizer-uprose-kings-county</t>
+  </si>
+  <si>
+    <t>Climate Program Associate</t>
+  </si>
+  <si>
+    <t>Institute for Agriculture and Trade Policy</t>
+  </si>
+  <si>
+    <t>Berlin, Berlin, DE</t>
+  </si>
+  <si>
+    <t>EUR 4000.00 - 5000.00/month</t>
+  </si>
+  <si>
+    <t>Climate Change, Agriculture, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5701ce0f30104e46adab583aa39601d1-climate-program-associate-institute-for-agriculture-and-trade-policy-berlin</t>
+  </si>
+  <si>
+    <t>Commercial Lending and Real Estate Development Manager</t>
+  </si>
+  <si>
+    <t>(LEDC MN) Latino Economic Development Center</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e80a3b835f6419fa89af4ee57ed96b5-commercial-lending-and-real-estate-development-manager-ledc-mn-latino-economic-development-center-saint-paul</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>The Advance Group</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5c23124177f3469e96d6ec3e41b8084b-communications-manager-the-advance-group-new-york</t>
+  </si>
+  <si>
+    <t>Community Manager</t>
+  </si>
+  <si>
+    <t>Rewriting the Code</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Science Technology, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53ac975af56f4f3e88614b9f7db8dcdb-community-manager-rewriting-the-code-durham</t>
+  </si>
+  <si>
+    <t>Community Operations Manager</t>
+  </si>
+  <si>
+    <t>South Benton Resource Center</t>
+  </si>
+  <si>
+    <t>Monroe, Oregon</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c3d1d74e72a4d2b871123085ccf6949-community-operations-manager-south-benton-resource-center-monroe</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Essie Justice Group</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/135048c3f811410c842c0764b84db522-community-organizer-essie-justice-group-los-angeles</t>
+  </si>
+  <si>
+    <t>Community Outreach Coordinator (Bilingual in Creole, Portuguese, Khmer, or Spanish)</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 28.88 - 28.88/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/117aadb3c1cc4fe1a0d3cbd80c0bd723-community-outreach-coordinator-bilingual-in-creole-portuguese-khmer-or-spanish-all-in-energy-brookline</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -679,15 +1195,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/04f0d0e1391d4d309a5895374cdae00d-controller-truckers-against-trafficking-englewood</t>
   </si>
   <si>
+    <t>CRM Lead</t>
+  </si>
+  <si>
+    <t>Mary's Meals USA</t>
+  </si>
+  <si>
+    <t>Bloomfield, NJ</t>
+  </si>
+  <si>
+    <t>Education, International Relations, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/beced4e868ab46fd97b9ec7fe16c9f52-crm-lead-marys-meals-usa-bloomfield</t>
+  </si>
+  <si>
+    <t>CTUL Lead Organizer (Bilingual English/Spanish)</t>
+  </si>
+  <si>
+    <t>Centro de Trabajadores Unidos En Lucha (CTUL)</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 77250.00 - 77250.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95883d45f8af44f59d521eb125f1c2de-ctul-lead-organizer-bilingual-englishspanish-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
     <t>Data Coordinator, Gifts &amp; Records (Office of Development)</t>
   </si>
   <si>
     <t>Mount Sinai Health System, New York</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 66482.07 - 85446.51/year</t>
   </si>
   <si>
@@ -697,15 +1243,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f2038ffd413a464b8cb6777a181fd1ce-data-coordinator-gifts-records-office-of-development-mount-sinai-health-system-new-york-new-york</t>
   </si>
   <si>
+    <t>Detainee Rights Project Lead</t>
+  </si>
+  <si>
+    <t>USD 72810.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11388e5f7f364888a492e2829104358f-detainee-rights-project-lead-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
     <t>Development Associate, Data and Operations</t>
   </si>
   <si>
     <t>Heading Home Inc.</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 26.75 - 28.40/hour</t>
   </si>
   <si>
@@ -715,6 +1270,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/a0d0301546a8416aa733f564679c2999-development-associate-data-and-operations-heading-home-inc-boston</t>
   </si>
   <si>
+    <t>Development Associate, Major Gifts at Lincoln Center Theater</t>
+  </si>
+  <si>
+    <t>Lincoln Center Theater - New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e96f27c5ed374edb86519b37d9f0c20c-development-associate-major-gifts-at-lincoln-center-theater-lincoln-center-theater-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Development Consultant RFP</t>
+  </si>
+  <si>
+    <t>Empowerment Avenue</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02df9b7f5fb046a8ac512dded64a9c4b-development-consultant-rfp-empowerment-avenue-oakland</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Mayor's Fund for Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9eb1289a42714d4f9de20da9e1acb142-development-coordinator-mayors-fund-for-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Development Manager (Fundraising Role)</t>
   </si>
   <si>
@@ -748,6 +1348,117 @@
     <t>https://www.idealist.org/en/nonprofit-job/16d4b808959642e6a97c6d5211e69f77-development-manager-and-writer-new-american-leaders-new-york</t>
   </si>
   <si>
+    <t>Direct Services and Program Coordinator</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Women, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91d6df5db385474bbd92a997444c2a7e-direct-services-and-program-coordinator-wv-free-charleston</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Reparations Stakeholder Authority of Evanston</t>
+  </si>
+  <si>
+    <t>Evanston, Illinois</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02a5fe2de3dd4407b5e2747001f64028-director-reparations-stakeholder-authority-of-evanston-evanston</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Interfaith Center on Corporate Responsibility</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/deba9935a69748faa1265d05eb761f9d-director-of-communications-interfaith-center-on-corporate-responsibility-new-york</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF COMMUNICATIONS &amp; MARKETING</t>
+  </si>
+  <si>
+    <t>Early Childhood Service Corps</t>
+  </si>
+  <si>
+    <t>Remote (Denver, Colorado)</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f577d944c0148c4aebd6b2f06a7dd6f-director-of-communications-marketing-early-childhood-service-corps-denver</t>
+  </si>
+  <si>
+    <t>Director of Conferences and Training</t>
+  </si>
+  <si>
+    <t>NATIONAL CONSUMER LAW CENTER®</t>
+  </si>
+  <si>
+    <t>USD 103500.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/babf3da6cd9042218bb849ab7c1d1342-director-of-conferences-and-training-national-consumer-law-center-boston</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36c9486ef21447baa6add7bffc58be81-director-of-conferences-and-training-national-consumer-law-center-boston</t>
+  </si>
+  <si>
+    <t>Director of Data and Technology</t>
+  </si>
+  <si>
+    <t>Chicago Abortion Fund</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 117000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9014d04d4a64f56ac963071af6480a4-director-of-data-and-technology-chicago-abortion-fund-chicago</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Project Access Now</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d9b9c566a8b44ef3b3801c3b5ca98d39-director-of-development-project-access-now-portland</t>
+  </si>
+  <si>
     <t>Director of Development and External Engagement</t>
   </si>
   <si>
@@ -772,21 +1483,126 @@
     <t>https://www.idealist.org/en/nonprofit-job/9cc930163c9446c8abb4e6d980a9e31b-director-of-finance-administration-urgent-action-fund-for-feminist-activism-alameda</t>
   </si>
   <si>
+    <t>Director of Finance &amp; Operations</t>
+  </si>
+  <si>
+    <t>Long Beach Museum of Art</t>
+  </si>
+  <si>
+    <t>Long Beach, California</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2dd4369396a4b25b93dd561ea55af2b-director-of-finance-operations-long-beach-museum-of-art-long-beach</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>USD 87550.00 - 87550.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f118fb0bd9a400aa4d075a22d42b9da-director-of-finance-and-operations-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
     <t>Director of Operations and Finance at Malkhut: A Progressive Jewish Spiritual Community in Western Queens</t>
   </si>
   <si>
     <t>Malkhut: progressive Jewish spirituality in Queens</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>Religion Spirituality</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/a86e83875f534e4f95ce445ef522e5dd-director-of-operations-and-finance-at-malkhut-a-progressive-jewish-spiritual-community-in-western-queens-malkhut-progressive-jewish-spirituality-in-queens-new-york</t>
   </si>
   <si>
+    <t>DIRECTOR OF PROGRAMMING</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9311257382a4771a73b96abf4e2493b-director-of-programming-early-childhood-service-corps-denver</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Chicago Recovery Alliance</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction, Mental Health, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86e4d9805890421981463dda39690398-director-of-programs-chicago-recovery-alliance-chicago</t>
+  </si>
+  <si>
+    <t>Director of Public Service, School of Law</t>
+  </si>
+  <si>
+    <t>University of Virginia</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5e97a7402c834e71966ceddcbef1d5d3-director-of-public-service-school-of-law-university-of-virginia-charlottesville</t>
+  </si>
+  <si>
+    <t>Director of Technology</t>
+  </si>
+  <si>
+    <t>The Gilder Lehrman Institute of American History</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dccd1e3a90b4f4981208a584f624982-director-of-technology-the-gilder-lehrman-institute-of-american-history-new-york</t>
+  </si>
+  <si>
+    <t>Director, Digital Fundraising</t>
+  </si>
+  <si>
+    <t>Amnesty International USA</t>
+  </si>
+  <si>
+    <t>USD 100199.00 - 130131.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4848b46647fe4b9d89e112b612908265-director-digital-fundraising-amnesty-international-usa-washington</t>
+  </si>
+  <si>
+    <t>Director, Finance Industry Partnerships</t>
+  </si>
+  <si>
+    <t>Financial Beginnings</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e075b2b20ca4cc78b1baf7e0fd985ac-director-finance-industry-partnerships-financial-beginnings-portland</t>
+  </si>
+  <si>
     <t>Director, Legal, Compliance &amp; Risk</t>
   </si>
   <si>
@@ -802,6 +1618,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/07acd4e3b7564ab8bc26c6ae65395c2d-director-legal-compliance-risk-pure-earthblacksmith-institute-new-york</t>
   </si>
   <si>
+    <t>Director, Research &amp; Prospect Management</t>
+  </si>
+  <si>
+    <t>American Museum Of Natural History</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4c9084d38ffc4a21a21398dd03078b93-director-research-prospect-management-american-museum-of-natural-history-new-york</t>
+  </si>
+  <si>
     <t>Dog Behavior Specialist</t>
   </si>
   <si>
@@ -811,6 +1639,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/8573de67614640219d0b96877ade910e-dog-behavior-specialist-orphans-of-the-storm-riverwoods</t>
   </si>
   <si>
+    <t>Equitable Climate Technology Market Research Analyst [CONTRACT]</t>
+  </si>
+  <si>
+    <t>VertueLab</t>
+  </si>
+  <si>
+    <t>Remote (Portland, Oregon)</t>
+  </si>
+  <si>
+    <t>USD 7000.00 - 7000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Science Technology, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2660313ba0542bda5cfbc6d2eef9f59-equitable-climate-technology-market-research-analyst-contract-vertuelab-portland</t>
+  </si>
+  <si>
+    <t>Especialista de Atracción de Talento</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 15750.00 - 15750.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73f15b5c6cdf4289a53aaf75e4260591-especialista-de-atraccion-de-talento-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
     <t>Executive Assistant, Development and Events</t>
   </si>
   <si>
@@ -826,6 +1693,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/0ebca73fe5e84a029a86a82386899d5a-executive-assistant-development-and-events-catholic-charities-archdiocese-of-ny-new-york</t>
   </si>
   <si>
+    <t>Executive Assistant, Office of the President</t>
+  </si>
+  <si>
+    <t>American Families for Vaccines</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca0bd49bbabf412d9112ab806fcdda55-executive-assistant-office-of-the-president-american-families-for-vaccines-portland</t>
+  </si>
+  <si>
+    <t>OPEN BOOKS</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8c753ca090140c59324d27c37f713eb-executive-director-open-books-chicago</t>
+  </si>
+  <si>
+    <t>External &amp; Media Relations Lead</t>
+  </si>
+  <si>
+    <t>Legal Voice</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c3d1ff20c47456ab24a8839c581a3d7-external-media-relations-lead-legal-voice-seattle</t>
+  </si>
+  <si>
+    <t>Facilitation &amp; Learning Manager</t>
+  </si>
+  <si>
+    <t>Citizen University</t>
+  </si>
+  <si>
+    <t>USD 72650.00 - 89950.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a573a931ba04139bc1fcf2b19d16de8-facilitation-learning-manager-citizen-university-seattle</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Darien Nature Center</t>
+  </si>
+  <si>
+    <t>Darien, Connecticut</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0dafb5cbf11549dba69f8e38f0dd7fe0-finance-manager-darien-nature-center-darien</t>
+  </si>
+  <si>
     <t>Grant Writer &amp; Pipeline Lead</t>
   </si>
   <si>
@@ -841,6 +1771,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c25566a1902648c5ae88ce48e6ec2063-grant-writer-pipeline-lead-art-start-inc-milwaukee</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c25566a1902648c5ae88ce48e6ec2063-grant-writer-pipeline-lead-art-start-inc-new-york</t>
+  </si>
+  <si>
+    <t>Grants Database Manager</t>
+  </si>
+  <si>
+    <t>DC Bar Foundation</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/54e1ddc2fac143e0a0a126107eb78879-grants-database-manager-dc-bar-foundation-washington</t>
+  </si>
+  <si>
     <t>Grants Manager</t>
   </si>
   <si>
@@ -850,21 +1795,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/7c74c08df8e445afb742c43f074ffd15-grants-manager-heading-home-inc-boston</t>
   </si>
   <si>
+    <t>Limitless Horizons Ixil</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/816ea13473e14db5b092a50d015e8bf7-grants-manager-limitless-horizons-ixil-canton-ilom-chajul</t>
+  </si>
+  <si>
+    <t>Group Leader [Bronx]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ceebdffc5d7147978ed069bbe16bf723-group-leader-bronx-replications-inc-bronx</t>
+  </si>
+  <si>
+    <t>Group Leader [Brooklyn]</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de8b98617b2d41dd8d10dacc18595e43-group-leader-brooklyn-replications-inc-brooklyn</t>
+  </si>
+  <si>
     <t>Growth &amp; Product Marketing Manager</t>
   </si>
   <si>
-    <t>Project Equity</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 92000.00/year</t>
   </si>
   <si>
-    <t>Community Development, Economic Development, Entrepreneurship</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/8d572001a3734d91a72335e580d98c3e-growth-product-marketing-manager-project-equity-oakland</t>
   </si>
   <si>
+    <t>HR and Compliance Director</t>
+  </si>
+  <si>
+    <t>Education &amp; Leadership Foundation</t>
+  </si>
+  <si>
+    <t>Fresno, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Job Workplace, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a12806b061ca4e3fab2c657f587d697f-hr-and-compliance-director-education-leadership-foundation-fresno</t>
+  </si>
+  <si>
     <t>Human Resources Assistant (Worcester, MA)</t>
   </si>
   <si>
@@ -883,6 +1876,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/5ae8b8ced3fa4d408a306e53848ff1e0-human-resources-assistant-worcester-ma-community-legal-aid-affiliate-worcester</t>
   </si>
   <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>Carolina Migrant Network</t>
+  </si>
+  <si>
+    <t>Remote (Charlotte, North Carolina)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f20c3fdfbcc4373980757658bbe0718-immigration-attorney-carolina-migrant-network-charlotte</t>
+  </si>
+  <si>
+    <t>IMPOWER Staff Attorney</t>
+  </si>
+  <si>
+    <t>National Immigration Project</t>
+  </si>
+  <si>
+    <t>USD 87181.00 - 97059.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cc8db3780414a2693f11ad6b57eaba8-impower-staff-attorney-national-immigration-project-washington</t>
+  </si>
+  <si>
+    <t>In-Custody Day Program Coordinator</t>
+  </si>
+  <si>
+    <t>The Gemma Project</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6752167c4dbf448db958104514e32925-in-custody-day-program-coordinator-the-gemma-project-oakland</t>
+  </si>
+  <si>
     <t>Intercultural Leadership and Project Development Coach</t>
   </si>
   <si>
@@ -898,6 +1939,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/fe84aef22a0c466fbf97b31614e3b671-intercultural-leadership-and-project-development-coach-the-marshall-legacy-institute-arlington</t>
   </si>
   <si>
+    <t>Internal Organizer</t>
+  </si>
+  <si>
+    <t>SEIU Healthcare IL IN MO KS</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 65380.00 - 69301.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a093d607d9b84dc496ddd1bed5746373-internal-organizer-seiu-healthcare-il-in-mo-ks-st-louis</t>
+  </si>
+  <si>
+    <t>USD 65380.00 - 89301.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9475ef3961364e5b9df8296aeda636bc-internal-organizer-seiu-healthcare-il-in-mo-ks-chicago</t>
+  </si>
+  <si>
     <t>Lead Analyst</t>
   </si>
   <si>
@@ -940,6 +2005,129 @@
     <t>https://www.idealist.org/en/nonprofit-job/b0d9c3d35ca2454eb6434776610db5de-legal-aid-staff-attorney-housing-worcester-community-legal-aid-affiliate-worcester</t>
   </si>
   <si>
+    <t>Legal Aid Staff Attorney Position in Staunton, Virginia</t>
+  </si>
+  <si>
+    <t>Blue Ridge Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Staunton, Virginia</t>
+  </si>
+  <si>
+    <t>USD 75384.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d1d742d47fe41b1bc9639eed9766e7d-legal-aid-staff-attorney-position-in-staunton-virginia-blue-ridge-legal-services-inc-staunton</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer {Director of Major Giving- Director level}</t>
+  </si>
+  <si>
+    <t>All Our Kin</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c3a3fe89cd74ddc85dcb2d907138afd-major-gifts-officer-director-of-major-giving-director-level-all-our-kin-new-haven</t>
+  </si>
+  <si>
+    <t>Manager, Member Engagement and Executive Operations</t>
+  </si>
+  <si>
+    <t>Media Impact Funders</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cd73d99a7e64ec7a29fd801af740cf9-manager-member-engagement-and-executive-operations-media-impact-funders-philadelphia</t>
+  </si>
+  <si>
+    <t>Managing Director</t>
+  </si>
+  <si>
+    <t>Dharmakaya Center for Wellbeing</t>
+  </si>
+  <si>
+    <t>Cragsmoor, New York</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bfb813189984b5cafd6ce5da73dc57f-managing-director-dharmakaya-center-for-wellbeing-cragsmoor</t>
+  </si>
+  <si>
+    <t>New England Area Coordinator</t>
+  </si>
+  <si>
+    <t>ASSE International Student Exchange</t>
+  </si>
+  <si>
+    <t>Remote (New Hampshire)</t>
+  </si>
+  <si>
+    <t>USD 18500.00 - 35000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/635674dc1d574a1180c474d5a79b7a70-new-england-area-coordinator-asse-international-student-exchange-portsmouth</t>
+  </si>
+  <si>
+    <t>NSD Senior Children's Counselor</t>
+  </si>
+  <si>
+    <t>Together for Youth</t>
+  </si>
+  <si>
+    <t>USD 21.25 - 23.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1300006e5c114b49beaf1b11aae142e3-nsd-senior-childrens-counselor-together-for-youth-albany</t>
+  </si>
+  <si>
+    <t>Operations Manager, Finance &amp; Operations</t>
+  </si>
+  <si>
+    <t>Bonneville Environmental Foundation (BEF)</t>
+  </si>
+  <si>
+    <t>USD 86007.00 - 100715.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/270bcb996bfc4abbae83cefceeeda6cf-operations-manager-finance-operations-bonneville-environmental-foundation-bef-portland</t>
+  </si>
+  <si>
+    <t>Parent Success Coach (Bilingual)</t>
+  </si>
+  <si>
+    <t>Hope Chicago</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc42d7366d564805adc1a5d908d52679-parent-success-coach-bilingual-hope-chicago-chicago</t>
+  </si>
+  <si>
     <t>Part-Time Nonprofit Operations / Office Manager</t>
   </si>
   <si>
@@ -958,6 +2146,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/84a2ac616e0a458ea65370cbd66e56c2-part-time-nonprofit-operations-office-manager-enroot-cambridge</t>
   </si>
   <si>
+    <t>Philanthropy Operations Specialist</t>
+  </si>
+  <si>
+    <t>ReSurge International</t>
+  </si>
+  <si>
+    <t>Sunnyvale, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, International Relations, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebb5760489f54c6b911872751f17d6cd-philanthropy-operations-specialist-resurge-international-sunnyvale</t>
+  </si>
+  <si>
+    <t>Policy Manager</t>
+  </si>
+  <si>
+    <t>Partnership for Children &amp; Youth</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Policy, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08d4780b0cda44a79214b1acfc1f38ce-policy-manager-partnership-for-children-youth-sacramento</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Xavier Mission Inc.</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 35000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bba199d7ef7a4879b87f880b8f90e2f2-program-assistant-xavier-mission-inc-new-york</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/596ce251e7644eaf9875dca8fdc5a316-program-assistant-east-side-house-settlement-bronx</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Institute for Contemporary Psychotherapy</t>
+  </si>
+  <si>
+    <t>USD 46800.00 - 51000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e86f0db4d04a486e91243eaeb920801a-program-coordinator-institute-for-contemporary-psychotherapy-new-york</t>
+  </si>
+  <si>
+    <t>Mott Philanthropic</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/dab4f44f9f8e447ea4567179f460acd9-program-coordinator-mott-philanthropic-boston</t>
+  </si>
+  <si>
     <t>Program Director</t>
   </si>
   <si>
@@ -967,15 +2242,108 @@
     <t>Austin, Texas</t>
   </si>
   <si>
-    <t>USD 75000.00/year</t>
-  </si>
-  <si>
     <t>Crime Safety, Disaster Relief, Rural Areas</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4766fedffeaf4b72a280c8493dd29185-program-director-texas-state-association-of-fire-emergency-districts-austin</t>
   </si>
   <si>
+    <t>Program Director (Friends of Lake Sammamish State Park)</t>
+  </si>
+  <si>
+    <t>Friends of Lake Sammamish State Park</t>
+  </si>
+  <si>
+    <t>Issaquah, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e4355bf10e94ecea8321aa0377bfb3f-program-director-friends-of-lake-sammamish-state-park-friends-of-lake-sammamish-state-park-issaquah</t>
+  </si>
+  <si>
+    <t>Program Specialist</t>
+  </si>
+  <si>
+    <t>Southwest Youth and Family Services</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/affc346a56d9431eaf0f3607f9d73515-program-specialist-southwest-youth-and-family-services-seattle</t>
+  </si>
+  <si>
+    <t>Programs Assistant_Cedar Evergreen</t>
+  </si>
+  <si>
+    <t>KidWorks</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a446456e084f436ab2ede655197fe051-programs-assistantcedar-evergreen-kidworks-santa-ana</t>
+  </si>
+  <si>
+    <t>PSICÓLOGX DE ATENCIÓN DIRECTA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c51d26d9dd974a899d53defb14f1f4c8-psicologx-de-atencion-directa-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
+    <t>Public Services Coordinator</t>
+  </si>
+  <si>
+    <t>New York Genealogical &amp; Biographical Society</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87908f1f9b78493680845d8bfe98ed0f-public-services-coordinator-new-york-genealogical-biographical-society-new-york</t>
+  </si>
+  <si>
+    <t>Regenerative Agriculture Program Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1f44ca1440145259f381029a670e5ff-regenerative-agriculture-program-manager-ledc-mn-latino-economic-development-center-saint-paul</t>
+  </si>
+  <si>
+    <t>Request for Conversation Legislative Tracking Consultant</t>
+  </si>
+  <si>
+    <t>Equality Federation</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e89ec1576fcb4f268cfb59b7f3e73dab-request-for-conversation-legislative-tracking-consultant-equality-federation-portland</t>
+  </si>
+  <si>
+    <t>Safe Routes to School (SRTS) Coordinator</t>
+  </si>
+  <si>
+    <t>p:ear</t>
+  </si>
+  <si>
+    <t>USD 75108.00 - 75108.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d589181678042a29ea238e31bb5ec44-safe-routes-to-school-srts-coordinator-pear-portland</t>
+  </si>
+  <si>
     <t>Salesforce &amp; Data Systems Specialist</t>
   </si>
   <si>
@@ -991,15 +2359,96 @@
     <t>https://www.idealist.org/en/nonprofit-job/8188faeae08846fc8a64d2ed73bbc19c-salesforce-data-systems-specialist-enroll-indy-indianapolis</t>
   </si>
   <si>
+    <t>Saturday Academy Facilitator (Contractual)</t>
+  </si>
+  <si>
+    <t>LINK Unlimited Scholars</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f70e81a8ac54544859ed168838a7f35-saturday-academy-facilitator-contractual-link-unlimited-scholars-chicago</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Appalachian Mountain Club</t>
+  </si>
+  <si>
+    <t>USD 57528.00 - 89265.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7835d90c6945478bbbf938078a931e21-senior-accountant-appalachian-mountain-club-boston</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Information Technology</t>
+  </si>
+  <si>
+    <t>PFLAG National</t>
+  </si>
+  <si>
+    <t>USD 67239.00 - 78188.00/year</t>
+  </si>
+  <si>
+    <t>Family, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1273b2250e604e4f9711737e7ebd021c-senior-coordinator-information-technology-pflag-national-washington</t>
+  </si>
+  <si>
+    <t>Senior Data and Analytics Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1baba8c8a6b2401aa78e320129398025-senior-data-and-analytics-manager-marys-meals-usa-bloomfield</t>
+  </si>
+  <si>
+    <t>Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, VA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b371e7d83e914d1686fe119aecf0fd1d-senior-energy-and-climate-analyst-piedmont-environmental-council-warrenton</t>
+  </si>
+  <si>
+    <t>Senior Finance and AP Analyst</t>
+  </si>
+  <si>
+    <t>American Society for Engineering Education</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef1c6a745ad14a7fb984b8c8d1c5b354-senior-finance-and-ap-analyst-american-society-for-engineering-education-washington</t>
+  </si>
+  <si>
+    <t>Senior Grants Manager</t>
+  </si>
+  <si>
+    <t>Way to Win</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b44ebfb106ce4d21b11eccd213a437ed-senior-grants-manager-way-to-win-washington</t>
+  </si>
+  <si>
     <t>Senior Grassroots Mobilization Organizer</t>
   </si>
   <si>
     <t>NETWORK Lobby for Catholic Social Justice</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 72000.00 - 89000.00/year</t>
   </si>
   <si>
@@ -1009,21 +2458,213 @@
     <t>https://www.idealist.org/en/nonprofit-job/cbd27488607b4a8e99ad3867f51bdad1-senior-grassroots-mobilization-organizer-network-lobby-for-catholic-social-justice-washington</t>
   </si>
   <si>
+    <t>Senior Individual Giving Officer / Major Gifts Officer (Part-Time)</t>
+  </si>
+  <si>
+    <t>LEAP Self-Defense</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d2b69cfc69e46eb88025ef397c7a43f-senior-individual-giving-officer-major-gifts-officer-part-time-leap-self-defense-boston</t>
+  </si>
+  <si>
+    <t>Senior Policy Counsel</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Florida</t>
+  </si>
+  <si>
+    <t>Tallahassee, Florida</t>
+  </si>
+  <si>
+    <t>USD 90200.00 - 110500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dff5f1dc7c6485aafcdf50c175a4a92-senior-policy-counsel-american-civil-liberties-union-of-florida-tallahassee</t>
+  </si>
+  <si>
+    <t>Senior Program Manager of Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>Literacy Partners, Inc.</t>
+  </si>
+  <si>
+    <t>USD 71250.00 - 74250.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e4b75f536bf46b7badbe18a41b0342e-senior-program-manager-of-strategic-partnerships-literacy-partners-inc-las-vegas</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51aa39e43ac94daf89f0759d0ccb6240-senior-program-manager-of-strategic-partnerships-literacy-partners-inc-san-diego</t>
+  </si>
+  <si>
+    <t>Service Coordinator (Livermore)</t>
+  </si>
+  <si>
+    <t>Satellite Affordable Housing Associates</t>
+  </si>
+  <si>
+    <t>Livermore, California</t>
+  </si>
+  <si>
+    <t>USD 31.25 - 36.06/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38eda31cd4114b16ba3b2dda3d4de55b-service-coordinator-livermore-satellite-affordable-housing-associates-livermore</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92769efffc7a44d69b2c632d18c9fb64-service-enriched-housing-super-hero-community-housing-resource-partners-inc-houston</t>
+  </si>
+  <si>
     <t>Software Developer</t>
   </si>
   <si>
     <t>Fishtank Learning</t>
   </si>
   <si>
-    <t>USD 75000.00 - 90000.00/year</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9e9fb09e9179468db6be577974ee9400-software-developer-fishtank-learning-boston</t>
   </si>
   <si>
+    <t>Solar Account Manager</t>
+  </si>
+  <si>
+    <t>RE-volv</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9dfce5ef83d440a8fb4fc574a4cc11e-solar-account-manager-re-volv-san-francisco</t>
+  </si>
+  <si>
+    <t>Sous Chef</t>
+  </si>
+  <si>
+    <t>International House at UC Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 76980.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a262d38c78e49fab6e0c7cc176c3639-sous-chef-international-house-at-uc-berkeley-berkeley</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9f49a469f6f4887a2f8201b72144451-staff-attorney-education-leadership-foundation-fresno</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Texas</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e962f76083ae484384a2f7857682f264-staff-attorney-american-civil-liberties-union-of-texas-dallas</t>
+  </si>
+  <si>
+    <t>Project on Predatory Student Lending</t>
+  </si>
+  <si>
+    <t>USD 125000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb5c95f66e4c46029534a2087028978b-staff-attorney-project-on-predatory-student-lending-boston</t>
+  </si>
+  <si>
+    <t>Staff Attorney (CA)</t>
+  </si>
+  <si>
+    <t>Disability Rights Advocates</t>
+  </si>
+  <si>
+    <t>USD 93627.00 - 116877.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d143e1eb7c884259bb218442ad06a18e-staff-attorney-ca-disability-rights-advocates-berkeley</t>
+  </si>
+  <si>
+    <t>Staff Attorney (NY)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/466d784c6dad4d348161d8a599595069-staff-attorney-ny-disability-rights-advocates-new-york</t>
+  </si>
+  <si>
+    <t>Strategic Advisor to the CEO</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a78e0ab2cb424965b921c83d09577cff-strategic-advisor-to-the-ceo-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Supervisor de Telemarketing</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles y Juveniles SOS de México, I. A. P</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 18500.00 - 19000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67b34fa73bd5424db68b851e519a567c-supervisor-de-telemarketing-aldeas-infantiles-y-juveniles-sos-de-mexico-i-a-p-ciudad-de-mexico</t>
+  </si>
+  <si>
     <t>Teacher Counselor</t>
   </si>
   <si>
@@ -1039,21 +2680,63 @@
     <t>https://www.idealist.org/en/job/859a535165fd4330877f7918cbb647c2-teacher-counselor-cambridge-housing-authority-cambridge</t>
   </si>
   <si>
+    <t>Temporary Admissions and Financial Aid Advisor (fixed term of up to approximately one year)</t>
+  </si>
+  <si>
+    <t>USD 71500.00 - 76500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/832d0e29e15c47bb9656334ca21e18cf-temporary-admissions-and-financial-aid-advisor-fixed-term-of-up-to-approximately-one-year-international-house-at-uc-berkeley-berkeley</t>
+  </si>
+  <si>
     <t>Temporary Family Law Staff Attorney</t>
   </si>
   <si>
     <t>Springfield, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 73000.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/fb69c5dbe4724340854b19e964899300-temporary-family-law-staff-attorney-community-legal-aid-affiliate-springfield</t>
   </si>
   <si>
+    <t>Temporary Part-Time Administrative Assistant</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dcd321e3ea844aba9b5539df9237dd6-temporary-part-time-administrative-assistant-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
+    <t>Training and Curriculum Manager</t>
+  </si>
+  <si>
+    <t>Northwest Resource Associates</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba3766b5147142d78de22a67a3f79e89-training-and-curriculum-manager-northwest-resource-associates-anchorage</t>
+  </si>
+  <si>
+    <t>Trial Attorney - LA County</t>
+  </si>
+  <si>
+    <t>BASTA Universal!</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8891d6641ad484997e26e191f809364-trial-attorney-la-county-basta-universal-los-angeles</t>
+  </si>
+  <si>
     <t>Two-Year Hub Manager, Emerging Issues</t>
   </si>
   <si>
@@ -1064,6 +2747,138 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/88015e8c020b469c92c37eecbbe34191-two-year-hub-manager-emerging-issues-earthjustice-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Finance and Business Affairs</t>
+  </si>
+  <si>
+    <t>The Partnership for Los Angeles Schools</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 173747.00 - 173747.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fadf07d48395440c9e097784fc5f1415-vice-president-of-finance-and-business-affairs-the-partnership-for-los-angeles-schools-los-angeles</t>
+  </si>
+  <si>
+    <t>Weatherization Program Coordinator</t>
+  </si>
+  <si>
+    <t>Civic Works</t>
+  </si>
+  <si>
+    <t>Baltimore, MD</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97e4a5843a48441cac4dd2e93f4b085a-weatherization-program-coordinator-civic-works-baltimore</t>
+  </si>
+  <si>
+    <t>Wolinsky Fellow</t>
+  </si>
+  <si>
+    <t>USD 88425.00 - 93627.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60e411f1137e40a4bad9986ee6ec4b22-wolinsky-fellow-disability-rights-advocates-chicago</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d5ba94644c24b6fa6119cf0a7fbb5b0-wolinsky-fellow-disability-rights-advocates-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1f4ebfdc366495d9c1f9e3361607991-wolinsky-fellow-disability-rights-advocates-berkeley</t>
+  </si>
+  <si>
+    <t>Worker Organizer</t>
+  </si>
+  <si>
+    <t>USD 61500.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af35996c064744c8a3b61074af061872-worker-organizer-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
+    <t>Workforce Partnerships and Talent Manager</t>
+  </si>
+  <si>
+    <t>EnCorps STEM Teachers Program</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92eefb414eec463592a6c7c430009d46-workforce-partnerships-and-talent-manager-encorps-stem-teachers-program-los-angeles</t>
+  </si>
+  <si>
+    <t>Wrentham Housing Authority - Executive Director</t>
+  </si>
+  <si>
+    <t>Massachusetts NAHRO</t>
+  </si>
+  <si>
+    <t>Wrentham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 61576.00 - 68418.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2374459068eb4941b9f0bfd9fc031159-wrentham-housing-authority-executive-director-massachusetts-nahro-wrentham</t>
+  </si>
+  <si>
+    <t>Youth Advocate - TGNC Women &amp; Femmes Focus</t>
+  </si>
+  <si>
+    <t>Lavender Youth Recreation and Information Center (LYRIC)</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 30.58 - 30.58/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f96b5229f17496e95cf47ca153e50aa-youth-advocate-tgnc-women-femmes-focus-lavender-youth-recreation-and-information-center-lyric-san-francisco</t>
+  </si>
+  <si>
+    <t>Youth Educator</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2953ce914d744aa18a4606482c4d9799-youth-educator-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Youth Organizer</t>
+  </si>
+  <si>
+    <t>Southeast Asian Community Alliance (SEACA)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f3246e7ea79a4972bdbee6a6c5914287-youth-organizer-southeast-asian-community-alliance-seaca-los-angeles</t>
   </si>
 </sst>
 </file>
@@ -2291,7 +4106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2330,8 +4145,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2339,7 +4204,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2380,738 +4245,3705 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="F3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
         <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
         <v>203</v>
       </c>
       <c r="E5" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="E7" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="F7" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E8" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F8" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D10" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E11" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F11" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B12" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F12" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="F13" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C14" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E15" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="F15" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="C16" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E16" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="F16" t="s">
-        <v>198</v>
+        <v>288</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="D17" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E17" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="F17" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
         <v>203</v>
       </c>
       <c r="E18" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="F18" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D19" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E19" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="F19" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B20" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>308</v>
       </c>
       <c r="D20" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E20" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="F20" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="F21" t="s">
-        <v>287</v>
+        <v>191</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E22" t="s">
-        <v>291</v>
+        <v>191</v>
       </c>
       <c r="F22" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="B23" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D23" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E23" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="F23" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="C24" t="s">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E24" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="F24" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="C25" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
       <c r="D25" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E25" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="F25" t="s">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="B26" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="C26" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="D26" t="s">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="E26" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="F26" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="C27" t="s">
-        <v>316</v>
+        <v>209</v>
       </c>
       <c r="D27" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E27" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="F27" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="C28" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="D28" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E28" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="F28" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="B29" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="C29" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="D29" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="F29" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>361</v>
       </c>
       <c r="D30" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E30" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="F30" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="B31" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>275</v>
       </c>
       <c r="E31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F31" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="B32" t="s">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="C32" t="s">
-        <v>342</v>
+        <v>209</v>
       </c>
       <c r="D32" t="s">
-        <v>343</v>
+        <v>203</v>
       </c>
       <c r="E32" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="F32" t="s">
-        <v>205</v>
+        <v>372</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B33" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>223</v>
+        <v>376</v>
       </c>
       <c r="D33" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="E33" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="F33" t="s">
+        <v>378</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>380</v>
+      </c>
+      <c r="B34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
+        <v>263</v>
+      </c>
+      <c r="F34" t="s">
+        <v>382</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>384</v>
+      </c>
+      <c r="B35" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" t="s">
+        <v>385</v>
+      </c>
+      <c r="D35" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" t="s">
+        <v>386</v>
+      </c>
+      <c r="F35" t="s">
+        <v>217</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>388</v>
+      </c>
+      <c r="B36" t="s">
+        <v>389</v>
+      </c>
+      <c r="C36" t="s">
+        <v>209</v>
+      </c>
+      <c r="D36" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" t="s">
+        <v>390</v>
+      </c>
+      <c r="F36" t="s">
+        <v>391</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>393</v>
+      </c>
+      <c r="B37" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" t="s">
+        <v>396</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>398</v>
+      </c>
+      <c r="B38" t="s">
+        <v>399</v>
+      </c>
+      <c r="C38" t="s">
+        <v>400</v>
+      </c>
+      <c r="D38" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" t="s">
+        <v>401</v>
+      </c>
+      <c r="F38" t="s">
+        <v>402</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>404</v>
+      </c>
+      <c r="B39" t="s">
+        <v>405</v>
+      </c>
+      <c r="C39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D39" t="s">
+        <v>203</v>
+      </c>
+      <c r="E39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F39" t="s">
+        <v>407</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>409</v>
+      </c>
+      <c r="B40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C40" t="s">
+        <v>298</v>
+      </c>
+      <c r="D40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E40" t="s">
+        <v>410</v>
+      </c>
+      <c r="F40" t="s">
+        <v>411</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>413</v>
+      </c>
+      <c r="B41" t="s">
+        <v>414</v>
+      </c>
+      <c r="C41" t="s">
+        <v>202</v>
+      </c>
+      <c r="D41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E41" t="s">
+        <v>415</v>
+      </c>
+      <c r="F41" t="s">
+        <v>416</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>418</v>
+      </c>
+      <c r="B42" t="s">
+        <v>419</v>
+      </c>
+      <c r="C42" t="s">
+        <v>367</v>
+      </c>
+      <c r="D42" t="s">
+        <v>203</v>
+      </c>
+      <c r="E42" t="s">
+        <v>420</v>
+      </c>
+      <c r="F42" t="s">
+        <v>421</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>423</v>
+      </c>
+      <c r="B43" t="s">
+        <v>424</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" t="s">
+        <v>275</v>
+      </c>
+      <c r="E43" t="s">
+        <v>425</v>
+      </c>
+      <c r="F43" t="s">
+        <v>426</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>428</v>
+      </c>
+      <c r="B44" t="s">
+        <v>429</v>
+      </c>
+      <c r="C44" t="s">
+        <v>226</v>
+      </c>
+      <c r="D44" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" t="s">
+        <v>430</v>
+      </c>
+      <c r="F44" t="s">
+        <v>431</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>433</v>
+      </c>
+      <c r="B45" t="s">
+        <v>434</v>
+      </c>
+      <c r="C45" t="s">
+        <v>435</v>
+      </c>
+      <c r="D45" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" t="s">
+        <v>436</v>
+      </c>
+      <c r="F45" t="s">
+        <v>437</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>439</v>
+      </c>
+      <c r="B46" t="s">
+        <v>440</v>
+      </c>
+      <c r="C46" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" t="s">
+        <v>441</v>
+      </c>
+      <c r="F46" t="s">
+        <v>442</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>444</v>
+      </c>
+      <c r="B47" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" t="s">
+        <v>445</v>
+      </c>
+      <c r="F47" t="s">
+        <v>446</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>448</v>
+      </c>
+      <c r="B48" t="s">
+        <v>449</v>
+      </c>
+      <c r="C48" t="s">
+        <v>450</v>
+      </c>
+      <c r="D48" t="s">
+        <v>203</v>
+      </c>
+      <c r="E48" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" t="s">
+        <v>451</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>453</v>
+      </c>
+      <c r="B49" t="s">
+        <v>454</v>
+      </c>
+      <c r="C49" t="s">
+        <v>209</v>
+      </c>
+      <c r="D49" t="s">
+        <v>203</v>
+      </c>
+      <c r="E49" t="s">
+        <v>455</v>
+      </c>
+      <c r="F49" t="s">
+        <v>456</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>458</v>
+      </c>
+      <c r="B50" t="s">
+        <v>459</v>
+      </c>
+      <c r="C50" t="s">
+        <v>460</v>
+      </c>
+      <c r="D50" t="s">
+        <v>461</v>
+      </c>
+      <c r="E50" t="s">
+        <v>462</v>
+      </c>
+      <c r="F50" t="s">
+        <v>463</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>465</v>
+      </c>
+      <c r="B51" t="s">
+        <v>466</v>
+      </c>
+      <c r="C51" t="s">
+        <v>209</v>
+      </c>
+      <c r="D51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E51" t="s">
+        <v>467</v>
+      </c>
+      <c r="F51" t="s">
+        <v>468</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>465</v>
+      </c>
+      <c r="B52" t="s">
+        <v>466</v>
+      </c>
+      <c r="C52" t="s">
+        <v>470</v>
+      </c>
+      <c r="D52" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" t="s">
+        <v>467</v>
+      </c>
+      <c r="F52" t="s">
+        <v>468</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>472</v>
+      </c>
+      <c r="B53" t="s">
+        <v>473</v>
+      </c>
+      <c r="C53" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" t="s">
+        <v>474</v>
+      </c>
+      <c r="F53" t="s">
+        <v>475</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>477</v>
+      </c>
+      <c r="B54" t="s">
+        <v>478</v>
+      </c>
+      <c r="C54" t="s">
+        <v>479</v>
+      </c>
+      <c r="D54" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" t="s">
+        <v>191</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>481</v>
+      </c>
+      <c r="B55" t="s">
+        <v>440</v>
+      </c>
+      <c r="C55" t="s">
+        <v>209</v>
+      </c>
+      <c r="D55" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" t="s">
+        <v>482</v>
+      </c>
+      <c r="F55" t="s">
+        <v>442</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>484</v>
+      </c>
+      <c r="B56" t="s">
+        <v>485</v>
+      </c>
+      <c r="C56" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" t="s">
+        <v>203</v>
+      </c>
+      <c r="E56" t="s">
+        <v>486</v>
+      </c>
+      <c r="F56" t="s">
+        <v>487</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>489</v>
+      </c>
+      <c r="B57" t="s">
+        <v>490</v>
+      </c>
+      <c r="C57" t="s">
+        <v>491</v>
+      </c>
+      <c r="D57" t="s">
+        <v>203</v>
+      </c>
+      <c r="E57" t="s">
+        <v>492</v>
+      </c>
+      <c r="F57" t="s">
+        <v>493</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>495</v>
+      </c>
+      <c r="B58" t="s">
+        <v>399</v>
+      </c>
+      <c r="C58" t="s">
+        <v>400</v>
+      </c>
+      <c r="D58" t="s">
+        <v>203</v>
+      </c>
+      <c r="E58" t="s">
+        <v>496</v>
+      </c>
+      <c r="F58" t="s">
+        <v>191</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" t="s">
+        <v>499</v>
+      </c>
+      <c r="C59" t="s">
+        <v>367</v>
+      </c>
+      <c r="D59" t="s">
+        <v>461</v>
+      </c>
+      <c r="E59" t="s">
+        <v>191</v>
+      </c>
+      <c r="F59" t="s">
+        <v>500</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>502</v>
+      </c>
+      <c r="B60" t="s">
+        <v>459</v>
+      </c>
+      <c r="C60" t="s">
+        <v>460</v>
+      </c>
+      <c r="D60" t="s">
+        <v>461</v>
+      </c>
+      <c r="E60" t="s">
+        <v>503</v>
+      </c>
+      <c r="F60" t="s">
+        <v>463</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>505</v>
+      </c>
+      <c r="B61" t="s">
+        <v>506</v>
+      </c>
+      <c r="C61" t="s">
+        <v>339</v>
+      </c>
+      <c r="D61" t="s">
+        <v>203</v>
+      </c>
+      <c r="E61" t="s">
+        <v>425</v>
+      </c>
+      <c r="F61" t="s">
+        <v>507</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>509</v>
+      </c>
+      <c r="B62" t="s">
+        <v>510</v>
+      </c>
+      <c r="C62" t="s">
+        <v>511</v>
+      </c>
+      <c r="D62" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" t="s">
+        <v>191</v>
+      </c>
+      <c r="F62" t="s">
+        <v>191</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>513</v>
+      </c>
+      <c r="B63" t="s">
+        <v>514</v>
+      </c>
+      <c r="C63" t="s">
+        <v>515</v>
+      </c>
+      <c r="D63" t="s">
+        <v>203</v>
+      </c>
+      <c r="E63" t="s">
+        <v>516</v>
+      </c>
+      <c r="F63" t="s">
+        <v>517</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>519</v>
+      </c>
+      <c r="B64" t="s">
+        <v>520</v>
+      </c>
+      <c r="C64" t="s">
+        <v>209</v>
+      </c>
+      <c r="D64" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" t="s">
+        <v>521</v>
+      </c>
+      <c r="F64" t="s">
+        <v>522</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>524</v>
+      </c>
+      <c r="B65" t="s">
+        <v>525</v>
+      </c>
+      <c r="C65" t="s">
+        <v>209</v>
+      </c>
+      <c r="D65" t="s">
+        <v>203</v>
+      </c>
+      <c r="E65" t="s">
+        <v>526</v>
+      </c>
+      <c r="F65" t="s">
+        <v>527</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>529</v>
+      </c>
+      <c r="B66" t="s">
+        <v>530</v>
+      </c>
+      <c r="C66" t="s">
+        <v>367</v>
+      </c>
+      <c r="D66" t="s">
+        <v>203</v>
+      </c>
+      <c r="E66" t="s">
+        <v>531</v>
+      </c>
+      <c r="F66" t="s">
+        <v>532</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>534</v>
+      </c>
+      <c r="B67" t="s">
+        <v>535</v>
+      </c>
+      <c r="C67" t="s">
+        <v>367</v>
+      </c>
+      <c r="D67" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" t="s">
+        <v>536</v>
+      </c>
+      <c r="F67" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>538</v>
+      </c>
+      <c r="B68" t="s">
+        <v>255</v>
+      </c>
+      <c r="C68" t="s">
+        <v>256</v>
+      </c>
+      <c r="D68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" t="s">
+        <v>539</v>
+      </c>
+      <c r="F68" t="s">
+        <v>258</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>541</v>
+      </c>
+      <c r="B69" t="s">
+        <v>542</v>
+      </c>
+      <c r="C69" t="s">
+        <v>543</v>
+      </c>
+      <c r="D69" t="s">
+        <v>275</v>
+      </c>
+      <c r="E69" t="s">
+        <v>544</v>
+      </c>
+      <c r="F69" t="s">
+        <v>545</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>547</v>
+      </c>
+      <c r="B70" t="s">
+        <v>548</v>
+      </c>
+      <c r="C70" t="s">
+        <v>549</v>
+      </c>
+      <c r="D70" t="s">
+        <v>550</v>
+      </c>
+      <c r="E70" t="s">
+        <v>551</v>
+      </c>
+      <c r="F70" t="s">
+        <v>552</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>554</v>
+      </c>
+      <c r="B71" t="s">
+        <v>555</v>
+      </c>
+      <c r="C71" t="s">
+        <v>367</v>
+      </c>
+      <c r="D71" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" t="s">
+        <v>556</v>
+      </c>
+      <c r="F71" t="s">
+        <v>557</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>559</v>
+      </c>
+      <c r="B72" t="s">
+        <v>560</v>
+      </c>
+      <c r="C72" t="s">
+        <v>209</v>
+      </c>
+      <c r="D72" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" t="s">
+        <v>204</v>
+      </c>
+      <c r="F72" t="s">
+        <v>191</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" t="s">
+        <v>562</v>
+      </c>
+      <c r="C73" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" t="s">
+        <v>203</v>
+      </c>
+      <c r="E73" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" t="s">
+        <v>563</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>565</v>
+      </c>
+      <c r="B74" t="s">
+        <v>566</v>
+      </c>
+      <c r="C74" t="s">
+        <v>209</v>
+      </c>
+      <c r="D74" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" t="s">
+        <v>567</v>
+      </c>
+      <c r="F74" t="s">
+        <v>568</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>570</v>
+      </c>
+      <c r="B75" t="s">
+        <v>571</v>
+      </c>
+      <c r="C75" t="s">
+        <v>209</v>
+      </c>
+      <c r="D75" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" t="s">
+        <v>572</v>
+      </c>
+      <c r="F75" t="s">
+        <v>573</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>575</v>
+      </c>
+      <c r="B76" t="s">
+        <v>576</v>
+      </c>
+      <c r="C76" t="s">
+        <v>577</v>
+      </c>
+      <c r="D76" t="s">
+        <v>461</v>
+      </c>
+      <c r="E76" t="s">
+        <v>539</v>
+      </c>
+      <c r="F76" t="s">
+        <v>578</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>580</v>
+      </c>
+      <c r="B77" t="s">
+        <v>581</v>
+      </c>
+      <c r="C77" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" t="s">
+        <v>275</v>
+      </c>
+      <c r="E77" t="s">
+        <v>582</v>
+      </c>
+      <c r="F77" t="s">
+        <v>583</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>580</v>
+      </c>
+      <c r="B78" t="s">
+        <v>581</v>
+      </c>
+      <c r="C78" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" t="s">
+        <v>275</v>
+      </c>
+      <c r="E78" t="s">
+        <v>582</v>
+      </c>
+      <c r="F78" t="s">
+        <v>583</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>586</v>
+      </c>
+      <c r="B79" t="s">
+        <v>587</v>
+      </c>
+      <c r="C79" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" t="s">
+        <v>203</v>
+      </c>
+      <c r="E79" t="s">
+        <v>588</v>
+      </c>
+      <c r="F79" t="s">
+        <v>191</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>590</v>
+      </c>
+      <c r="B80" t="s">
+        <v>414</v>
+      </c>
+      <c r="C80" t="s">
+        <v>202</v>
+      </c>
+      <c r="D80" t="s">
+        <v>203</v>
+      </c>
+      <c r="E80" t="s">
+        <v>591</v>
+      </c>
+      <c r="F80" t="s">
+        <v>416</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>590</v>
+      </c>
+      <c r="B81" t="s">
+        <v>593</v>
+      </c>
+      <c r="C81" t="s">
+        <v>209</v>
+      </c>
+      <c r="D81" t="s">
+        <v>275</v>
+      </c>
+      <c r="E81" t="s">
+        <v>191</v>
+      </c>
+      <c r="F81" t="s">
+        <v>594</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>596</v>
+      </c>
+      <c r="B82" t="s">
+        <v>597</v>
+      </c>
+      <c r="C82" t="s">
+        <v>598</v>
+      </c>
+      <c r="D82" t="s">
+        <v>461</v>
+      </c>
+      <c r="E82" t="s">
+        <v>599</v>
+      </c>
+      <c r="F82" t="s">
+        <v>600</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>602</v>
+      </c>
+      <c r="B83" t="s">
+        <v>597</v>
+      </c>
+      <c r="C83" t="s">
+        <v>603</v>
+      </c>
+      <c r="D83" t="s">
+        <v>461</v>
+      </c>
+      <c r="E83" t="s">
+        <v>599</v>
+      </c>
+      <c r="F83" t="s">
+        <v>600</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>605</v>
+      </c>
+      <c r="B84" t="s">
+        <v>238</v>
+      </c>
+      <c r="C84" t="s">
+        <v>209</v>
+      </c>
+      <c r="D84" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" t="s">
+        <v>606</v>
+      </c>
+      <c r="F84" t="s">
+        <v>240</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>608</v>
+      </c>
+      <c r="B85" t="s">
+        <v>609</v>
+      </c>
+      <c r="C85" t="s">
+        <v>610</v>
+      </c>
+      <c r="D85" t="s">
+        <v>203</v>
+      </c>
+      <c r="E85" t="s">
+        <v>611</v>
+      </c>
+      <c r="F85" t="s">
+        <v>612</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>614</v>
+      </c>
+      <c r="B86" t="s">
+        <v>615</v>
+      </c>
+      <c r="C86" t="s">
+        <v>616</v>
+      </c>
+      <c r="D86" t="s">
+        <v>203</v>
+      </c>
+      <c r="E86" t="s">
+        <v>617</v>
+      </c>
+      <c r="F86" t="s">
+        <v>618</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>620</v>
+      </c>
+      <c r="B87" t="s">
+        <v>621</v>
+      </c>
+      <c r="C87" t="s">
+        <v>622</v>
+      </c>
+      <c r="D87" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" t="s">
+        <v>623</v>
+      </c>
+      <c r="F87" t="s">
+        <v>624</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>626</v>
+      </c>
+      <c r="B88" t="s">
+        <v>627</v>
+      </c>
+      <c r="C88" t="s">
+        <v>209</v>
+      </c>
+      <c r="D88" t="s">
+        <v>550</v>
+      </c>
+      <c r="E88" t="s">
+        <v>628</v>
+      </c>
+      <c r="F88" t="s">
+        <v>629</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>631</v>
+      </c>
+      <c r="B89" t="s">
+        <v>632</v>
+      </c>
+      <c r="C89" t="s">
+        <v>633</v>
+      </c>
+      <c r="D89" t="s">
+        <v>203</v>
+      </c>
+      <c r="E89" t="s">
+        <v>634</v>
+      </c>
+      <c r="F89" t="s">
+        <v>191</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>636</v>
+      </c>
+      <c r="B90" t="s">
+        <v>637</v>
+      </c>
+      <c r="C90" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" t="s">
+        <v>275</v>
+      </c>
+      <c r="E90" t="s">
+        <v>638</v>
+      </c>
+      <c r="F90" t="s">
+        <v>639</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>641</v>
+      </c>
+      <c r="B91" t="s">
+        <v>642</v>
+      </c>
+      <c r="C91" t="s">
+        <v>643</v>
+      </c>
+      <c r="D91" t="s">
+        <v>203</v>
+      </c>
+      <c r="E91" t="s">
+        <v>644</v>
+      </c>
+      <c r="F91" t="s">
+        <v>645</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>641</v>
+      </c>
+      <c r="B92" t="s">
+        <v>642</v>
+      </c>
+      <c r="C92" t="s">
+        <v>339</v>
+      </c>
+      <c r="D92" t="s">
+        <v>203</v>
+      </c>
+      <c r="E92" t="s">
+        <v>647</v>
+      </c>
+      <c r="F92" t="s">
+        <v>645</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>649</v>
+      </c>
+      <c r="B93" t="s">
+        <v>650</v>
+      </c>
+      <c r="C93" t="s">
+        <v>209</v>
+      </c>
+      <c r="D93" t="s">
+        <v>203</v>
+      </c>
+      <c r="E93" t="s">
+        <v>651</v>
+      </c>
+      <c r="F93" t="s">
+        <v>652</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>654</v>
+      </c>
+      <c r="B94" t="s">
+        <v>655</v>
+      </c>
+      <c r="C94" t="s">
+        <v>656</v>
+      </c>
+      <c r="D94" t="s">
+        <v>203</v>
+      </c>
+      <c r="E94" t="s">
+        <v>657</v>
+      </c>
+      <c r="F94" t="s">
+        <v>658</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>660</v>
+      </c>
+      <c r="B95" t="s">
+        <v>615</v>
+      </c>
+      <c r="C95" t="s">
+        <v>616</v>
+      </c>
+      <c r="D95" t="s">
+        <v>203</v>
+      </c>
+      <c r="E95" t="s">
+        <v>661</v>
+      </c>
+      <c r="F95" t="s">
+        <v>191</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>663</v>
+      </c>
+      <c r="B96" t="s">
+        <v>664</v>
+      </c>
+      <c r="C96" t="s">
+        <v>665</v>
+      </c>
+      <c r="D96" t="s">
+        <v>203</v>
+      </c>
+      <c r="E96" t="s">
+        <v>666</v>
+      </c>
+      <c r="F96" t="s">
+        <v>667</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>669</v>
+      </c>
+      <c r="B97" t="s">
+        <v>670</v>
+      </c>
+      <c r="C97" t="s">
+        <v>671</v>
+      </c>
+      <c r="D97" t="s">
+        <v>203</v>
+      </c>
+      <c r="E97" t="s">
+        <v>672</v>
+      </c>
+      <c r="F97" t="s">
+        <v>673</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>675</v>
+      </c>
+      <c r="B98" t="s">
+        <v>676</v>
+      </c>
+      <c r="C98" t="s">
+        <v>209</v>
+      </c>
+      <c r="D98" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" t="s">
+        <v>677</v>
+      </c>
+      <c r="F98" t="s">
+        <v>678</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>680</v>
+      </c>
+      <c r="B99" t="s">
+        <v>681</v>
+      </c>
+      <c r="C99" t="s">
+        <v>682</v>
+      </c>
+      <c r="D99" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" t="s">
+        <v>204</v>
+      </c>
+      <c r="F99" t="s">
+        <v>683</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>685</v>
+      </c>
+      <c r="B100" t="s">
+        <v>686</v>
+      </c>
+      <c r="C100" t="s">
+        <v>687</v>
+      </c>
+      <c r="D100" t="s">
+        <v>275</v>
+      </c>
+      <c r="E100" t="s">
+        <v>688</v>
+      </c>
+      <c r="F100" t="s">
+        <v>673</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>690</v>
+      </c>
+      <c r="B101" t="s">
+        <v>691</v>
+      </c>
+      <c r="C101" t="s">
+        <v>280</v>
+      </c>
+      <c r="D101" t="s">
+        <v>203</v>
+      </c>
+      <c r="E101" t="s">
+        <v>692</v>
+      </c>
+      <c r="F101" t="s">
+        <v>693</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>695</v>
+      </c>
+      <c r="B102" t="s">
+        <v>696</v>
+      </c>
+      <c r="C102" t="s">
+        <v>479</v>
+      </c>
+      <c r="D102" t="s">
+        <v>203</v>
+      </c>
+      <c r="E102" t="s">
+        <v>697</v>
+      </c>
+      <c r="F102" t="s">
+        <v>217</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>699</v>
+      </c>
+      <c r="B103" t="s">
+        <v>700</v>
+      </c>
+      <c r="C103" t="s">
+        <v>339</v>
+      </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
+      <c r="E103" t="s">
+        <v>701</v>
+      </c>
+      <c r="F103" t="s">
+        <v>702</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>704</v>
+      </c>
+      <c r="B104" t="s">
+        <v>705</v>
+      </c>
+      <c r="C104" t="s">
+        <v>706</v>
+      </c>
+      <c r="D104" t="s">
+        <v>461</v>
+      </c>
+      <c r="E104" t="s">
+        <v>707</v>
+      </c>
+      <c r="F104" t="s">
+        <v>708</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B105" t="s">
+        <v>711</v>
+      </c>
+      <c r="C105" t="s">
+        <v>712</v>
+      </c>
+      <c r="D105" t="s">
+        <v>203</v>
+      </c>
+      <c r="E105" t="s">
+        <v>713</v>
+      </c>
+      <c r="F105" t="s">
+        <v>714</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>716</v>
+      </c>
+      <c r="B106" t="s">
+        <v>717</v>
+      </c>
+      <c r="C106" t="s">
+        <v>718</v>
+      </c>
+      <c r="D106" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" t="s">
+        <v>719</v>
+      </c>
+      <c r="F106" t="s">
+        <v>720</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>722</v>
+      </c>
+      <c r="B107" t="s">
+        <v>723</v>
+      </c>
+      <c r="C107" t="s">
+        <v>367</v>
+      </c>
+      <c r="D107" t="s">
+        <v>461</v>
+      </c>
+      <c r="E107" t="s">
+        <v>724</v>
+      </c>
+      <c r="F107" t="s">
+        <v>725</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>722</v>
+      </c>
+      <c r="B108" t="s">
+        <v>231</v>
+      </c>
+      <c r="C108" t="s">
+        <v>727</v>
+      </c>
+      <c r="D108" t="s">
+        <v>550</v>
+      </c>
+      <c r="E108" t="s">
+        <v>728</v>
+      </c>
+      <c r="F108" t="s">
+        <v>235</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>730</v>
+      </c>
+      <c r="B109" t="s">
+        <v>731</v>
+      </c>
+      <c r="C109" t="s">
+        <v>367</v>
+      </c>
+      <c r="D109" t="s">
+        <v>203</v>
+      </c>
+      <c r="E109" t="s">
+        <v>732</v>
+      </c>
+      <c r="F109" t="s">
+        <v>733</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>730</v>
+      </c>
+      <c r="B110" t="s">
+        <v>735</v>
+      </c>
+      <c r="C110" t="s">
+        <v>470</v>
+      </c>
+      <c r="D110" t="s">
+        <v>203</v>
+      </c>
+      <c r="E110" t="s">
+        <v>736</v>
+      </c>
+      <c r="F110" t="s">
+        <v>737</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>739</v>
+      </c>
+      <c r="B111" t="s">
+        <v>740</v>
+      </c>
+      <c r="C111" t="s">
+        <v>741</v>
+      </c>
+      <c r="D111" t="s">
+        <v>203</v>
+      </c>
+      <c r="E111" t="s">
+        <v>425</v>
+      </c>
+      <c r="F111" t="s">
+        <v>742</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>744</v>
+      </c>
+      <c r="B112" t="s">
+        <v>745</v>
+      </c>
+      <c r="C112" t="s">
+        <v>746</v>
+      </c>
+      <c r="D112" t="s">
+        <v>275</v>
+      </c>
+      <c r="E112" t="s">
+        <v>747</v>
+      </c>
+      <c r="F112" t="s">
+        <v>748</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>750</v>
+      </c>
+      <c r="B113" t="s">
+        <v>751</v>
+      </c>
+      <c r="C113" t="s">
+        <v>323</v>
+      </c>
+      <c r="D113" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" t="s">
+        <v>752</v>
+      </c>
+      <c r="F113" t="s">
+        <v>673</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>754</v>
+      </c>
+      <c r="B114" t="s">
+        <v>755</v>
+      </c>
+      <c r="C114" t="s">
+        <v>756</v>
+      </c>
+      <c r="D114" t="s">
+        <v>461</v>
+      </c>
+      <c r="E114" t="s">
+        <v>757</v>
+      </c>
+      <c r="F114" t="s">
+        <v>600</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>759</v>
+      </c>
+      <c r="B115" t="s">
+        <v>548</v>
+      </c>
+      <c r="C115" t="s">
+        <v>549</v>
+      </c>
+      <c r="D115" t="s">
+        <v>550</v>
+      </c>
+      <c r="E115" t="s">
+        <v>551</v>
+      </c>
+      <c r="F115" t="s">
+        <v>552</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>761</v>
+      </c>
+      <c r="B116" t="s">
+        <v>762</v>
+      </c>
+      <c r="C116" t="s">
+        <v>367</v>
+      </c>
+      <c r="D116" t="s">
+        <v>203</v>
+      </c>
+      <c r="E116" t="s">
+        <v>763</v>
+      </c>
+      <c r="F116" t="s">
+        <v>228</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>765</v>
+      </c>
+      <c r="B117" t="s">
+        <v>360</v>
+      </c>
+      <c r="C117" t="s">
+        <v>361</v>
+      </c>
+      <c r="D117" t="s">
+        <v>203</v>
+      </c>
+      <c r="E117" t="s">
+        <v>713</v>
+      </c>
+      <c r="F117" t="s">
+        <v>363</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>767</v>
+      </c>
+      <c r="B118" t="s">
+        <v>768</v>
+      </c>
+      <c r="C118" t="s">
+        <v>209</v>
+      </c>
+      <c r="D118" t="s">
+        <v>275</v>
+      </c>
+      <c r="E118" t="s">
+        <v>539</v>
+      </c>
+      <c r="F118" t="s">
+        <v>769</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>771</v>
+      </c>
+      <c r="B119" t="s">
+        <v>772</v>
+      </c>
+      <c r="C119" t="s">
+        <v>479</v>
+      </c>
+      <c r="D119" t="s">
+        <v>203</v>
+      </c>
+      <c r="E119" t="s">
+        <v>773</v>
+      </c>
+      <c r="F119" t="s">
+        <v>774</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>776</v>
+      </c>
+      <c r="B120" t="s">
+        <v>777</v>
+      </c>
+      <c r="C120" t="s">
+        <v>778</v>
+      </c>
+      <c r="D120" t="s">
+        <v>203</v>
+      </c>
+      <c r="E120" t="s">
+        <v>617</v>
+      </c>
+      <c r="F120" t="s">
+        <v>779</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>781</v>
+      </c>
+      <c r="B121" t="s">
+        <v>782</v>
+      </c>
+      <c r="C121" t="s">
+        <v>339</v>
+      </c>
+      <c r="D121" t="s">
+        <v>275</v>
+      </c>
+      <c r="E121" t="s">
+        <v>191</v>
+      </c>
+      <c r="F121" t="s">
         <v>205</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>349</v>
+      <c r="H121" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>784</v>
+      </c>
+      <c r="B122" t="s">
+        <v>785</v>
+      </c>
+      <c r="C122" t="s">
+        <v>202</v>
+      </c>
+      <c r="D122" t="s">
+        <v>203</v>
+      </c>
+      <c r="E122" t="s">
+        <v>786</v>
+      </c>
+      <c r="F122" t="s">
+        <v>787</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>789</v>
+      </c>
+      <c r="B123" t="s">
+        <v>790</v>
+      </c>
+      <c r="C123" t="s">
+        <v>221</v>
+      </c>
+      <c r="D123" t="s">
+        <v>203</v>
+      </c>
+      <c r="E123" t="s">
+        <v>791</v>
+      </c>
+      <c r="F123" t="s">
+        <v>792</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>794</v>
+      </c>
+      <c r="B124" t="s">
+        <v>394</v>
+      </c>
+      <c r="C124" t="s">
+        <v>395</v>
+      </c>
+      <c r="D124" t="s">
+        <v>203</v>
+      </c>
+      <c r="E124" t="s">
+        <v>191</v>
+      </c>
+      <c r="F124" t="s">
+        <v>396</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>194</v>
+      </c>
+      <c r="B125" t="s">
+        <v>796</v>
+      </c>
+      <c r="C125" t="s">
+        <v>797</v>
+      </c>
+      <c r="D125" t="s">
+        <v>203</v>
+      </c>
+      <c r="E125" t="s">
+        <v>798</v>
+      </c>
+      <c r="F125" t="s">
+        <v>799</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>801</v>
+      </c>
+      <c r="B126" t="s">
+        <v>802</v>
+      </c>
+      <c r="C126" t="s">
+        <v>803</v>
+      </c>
+      <c r="D126" t="s">
+        <v>203</v>
+      </c>
+      <c r="E126" t="s">
+        <v>436</v>
+      </c>
+      <c r="F126" t="s">
+        <v>329</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>805</v>
+      </c>
+      <c r="B127" t="s">
+        <v>806</v>
+      </c>
+      <c r="C127" t="s">
+        <v>209</v>
+      </c>
+      <c r="D127" t="s">
+        <v>203</v>
+      </c>
+      <c r="E127" t="s">
+        <v>807</v>
+      </c>
+      <c r="F127" t="s">
+        <v>191</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>809</v>
+      </c>
+      <c r="B128" t="s">
+        <v>810</v>
+      </c>
+      <c r="C128" t="s">
+        <v>221</v>
+      </c>
+      <c r="D128" t="s">
+        <v>203</v>
+      </c>
+      <c r="E128" t="s">
+        <v>811</v>
+      </c>
+      <c r="F128" t="s">
+        <v>812</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>814</v>
+      </c>
+      <c r="B129" t="s">
+        <v>815</v>
+      </c>
+      <c r="C129" t="s">
+        <v>202</v>
+      </c>
+      <c r="D129" t="s">
+        <v>461</v>
+      </c>
+      <c r="E129" t="s">
+        <v>816</v>
+      </c>
+      <c r="F129" t="s">
+        <v>563</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>818</v>
+      </c>
+      <c r="B130" t="s">
+        <v>819</v>
+      </c>
+      <c r="C130" t="s">
+        <v>820</v>
+      </c>
+      <c r="D130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E130" t="s">
+        <v>821</v>
+      </c>
+      <c r="F130" t="s">
+        <v>391</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>823</v>
+      </c>
+      <c r="B131" t="s">
+        <v>824</v>
+      </c>
+      <c r="C131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D131" t="s">
+        <v>203</v>
+      </c>
+      <c r="E131" t="s">
+        <v>825</v>
+      </c>
+      <c r="F131" t="s">
+        <v>826</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>823</v>
+      </c>
+      <c r="B132" t="s">
+        <v>824</v>
+      </c>
+      <c r="C132" t="s">
+        <v>828</v>
+      </c>
+      <c r="D132" t="s">
+        <v>203</v>
+      </c>
+      <c r="E132" t="s">
+        <v>825</v>
+      </c>
+      <c r="F132" t="s">
+        <v>826</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>830</v>
+      </c>
+      <c r="B133" t="s">
+        <v>831</v>
+      </c>
+      <c r="C133" t="s">
+        <v>832</v>
+      </c>
+      <c r="D133" t="s">
+        <v>203</v>
+      </c>
+      <c r="E133" t="s">
+        <v>833</v>
+      </c>
+      <c r="F133" t="s">
+        <v>834</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>836</v>
+      </c>
+      <c r="B134" t="s">
+        <v>837</v>
+      </c>
+      <c r="C134" t="s">
+        <v>838</v>
+      </c>
+      <c r="D134" t="s">
+        <v>461</v>
+      </c>
+      <c r="E134" t="s">
+        <v>839</v>
+      </c>
+      <c r="F134" t="s">
+        <v>840</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>842</v>
+      </c>
+      <c r="B135" t="s">
+        <v>843</v>
+      </c>
+      <c r="C135" t="s">
+        <v>209</v>
+      </c>
+      <c r="D135" t="s">
+        <v>203</v>
+      </c>
+      <c r="E135" t="s">
+        <v>713</v>
+      </c>
+      <c r="F135" t="s">
+        <v>329</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>845</v>
+      </c>
+      <c r="B136" t="s">
+        <v>846</v>
+      </c>
+      <c r="C136" t="s">
+        <v>209</v>
+      </c>
+      <c r="D136" t="s">
+        <v>203</v>
+      </c>
+      <c r="E136" t="s">
+        <v>847</v>
+      </c>
+      <c r="F136" t="s">
+        <v>848</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>850</v>
+      </c>
+      <c r="B137" t="s">
+        <v>851</v>
+      </c>
+      <c r="C137" t="s">
+        <v>852</v>
+      </c>
+      <c r="D137" t="s">
+        <v>203</v>
+      </c>
+      <c r="E137" t="s">
+        <v>853</v>
+      </c>
+      <c r="F137" t="s">
+        <v>329</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>855</v>
+      </c>
+      <c r="B138" t="s">
+        <v>609</v>
+      </c>
+      <c r="C138" t="s">
+        <v>610</v>
+      </c>
+      <c r="D138" t="s">
+        <v>203</v>
+      </c>
+      <c r="E138" t="s">
+        <v>856</v>
+      </c>
+      <c r="F138" t="s">
+        <v>629</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>855</v>
+      </c>
+      <c r="B139" t="s">
+        <v>858</v>
+      </c>
+      <c r="C139" t="s">
+        <v>859</v>
+      </c>
+      <c r="D139" t="s">
+        <v>203</v>
+      </c>
+      <c r="E139" t="s">
+        <v>191</v>
+      </c>
+      <c r="F139" t="s">
+        <v>391</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>855</v>
+      </c>
+      <c r="B140" t="s">
+        <v>861</v>
+      </c>
+      <c r="C140" t="s">
+        <v>209</v>
+      </c>
+      <c r="D140" t="s">
+        <v>203</v>
+      </c>
+      <c r="E140" t="s">
+        <v>862</v>
+      </c>
+      <c r="F140" t="s">
+        <v>863</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>865</v>
+      </c>
+      <c r="B141" t="s">
+        <v>866</v>
+      </c>
+      <c r="C141" t="s">
+        <v>852</v>
+      </c>
+      <c r="D141" t="s">
+        <v>203</v>
+      </c>
+      <c r="E141" t="s">
+        <v>867</v>
+      </c>
+      <c r="F141" t="s">
+        <v>868</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>870</v>
+      </c>
+      <c r="B142" t="s">
+        <v>866</v>
+      </c>
+      <c r="C142" t="s">
+        <v>367</v>
+      </c>
+      <c r="D142" t="s">
+        <v>203</v>
+      </c>
+      <c r="E142" t="s">
+        <v>867</v>
+      </c>
+      <c r="F142" t="s">
+        <v>868</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>872</v>
+      </c>
+      <c r="B143" t="s">
+        <v>873</v>
+      </c>
+      <c r="C143" t="s">
+        <v>367</v>
+      </c>
+      <c r="D143" t="s">
+        <v>203</v>
+      </c>
+      <c r="E143" t="s">
+        <v>874</v>
+      </c>
+      <c r="F143" t="s">
+        <v>875</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>877</v>
+      </c>
+      <c r="B144" t="s">
+        <v>878</v>
+      </c>
+      <c r="C144" t="s">
+        <v>879</v>
+      </c>
+      <c r="D144" t="s">
+        <v>203</v>
+      </c>
+      <c r="E144" t="s">
+        <v>880</v>
+      </c>
+      <c r="F144" t="s">
+        <v>881</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>883</v>
+      </c>
+      <c r="B145" t="s">
+        <v>884</v>
+      </c>
+      <c r="C145" t="s">
+        <v>885</v>
+      </c>
+      <c r="D145" t="s">
+        <v>203</v>
+      </c>
+      <c r="E145" t="s">
+        <v>886</v>
+      </c>
+      <c r="F145" t="s">
+        <v>191</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>888</v>
+      </c>
+      <c r="B146" t="s">
+        <v>851</v>
+      </c>
+      <c r="C146" t="s">
+        <v>852</v>
+      </c>
+      <c r="D146" t="s">
+        <v>550</v>
+      </c>
+      <c r="E146" t="s">
+        <v>889</v>
+      </c>
+      <c r="F146" t="s">
+        <v>329</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>891</v>
+      </c>
+      <c r="B147" t="s">
+        <v>615</v>
+      </c>
+      <c r="C147" t="s">
+        <v>892</v>
+      </c>
+      <c r="D147" t="s">
+        <v>550</v>
+      </c>
+      <c r="E147" t="s">
+        <v>893</v>
+      </c>
+      <c r="F147" t="s">
+        <v>191</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>895</v>
+      </c>
+      <c r="B148" t="s">
+        <v>399</v>
+      </c>
+      <c r="C148" t="s">
+        <v>400</v>
+      </c>
+      <c r="D148" t="s">
+        <v>233</v>
+      </c>
+      <c r="E148" t="s">
+        <v>191</v>
+      </c>
+      <c r="F148" t="s">
+        <v>191</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>897</v>
+      </c>
+      <c r="B149" t="s">
+        <v>898</v>
+      </c>
+      <c r="C149" t="s">
+        <v>899</v>
+      </c>
+      <c r="D149" t="s">
+        <v>203</v>
+      </c>
+      <c r="E149" t="s">
+        <v>900</v>
+      </c>
+      <c r="F149" t="s">
+        <v>191</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>902</v>
+      </c>
+      <c r="B150" t="s">
+        <v>903</v>
+      </c>
+      <c r="C150" t="s">
+        <v>226</v>
+      </c>
+      <c r="D150" t="s">
+        <v>203</v>
+      </c>
+      <c r="E150" t="s">
+        <v>904</v>
+      </c>
+      <c r="F150" t="s">
+        <v>905</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>907</v>
+      </c>
+      <c r="B151" t="s">
+        <v>908</v>
+      </c>
+      <c r="C151" t="s">
+        <v>367</v>
+      </c>
+      <c r="D151" t="s">
+        <v>203</v>
+      </c>
+      <c r="E151" t="s">
+        <v>909</v>
+      </c>
+      <c r="F151" t="s">
+        <v>191</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>911</v>
+      </c>
+      <c r="B152" t="s">
+        <v>912</v>
+      </c>
+      <c r="C152" t="s">
+        <v>913</v>
+      </c>
+      <c r="D152" t="s">
+        <v>203</v>
+      </c>
+      <c r="E152" t="s">
+        <v>914</v>
+      </c>
+      <c r="F152" t="s">
+        <v>205</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>916</v>
+      </c>
+      <c r="B153" t="s">
+        <v>917</v>
+      </c>
+      <c r="C153" t="s">
+        <v>918</v>
+      </c>
+      <c r="D153" t="s">
+        <v>203</v>
+      </c>
+      <c r="E153" t="s">
+        <v>919</v>
+      </c>
+      <c r="F153" t="s">
+        <v>920</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>922</v>
+      </c>
+      <c r="B154" t="s">
+        <v>866</v>
+      </c>
+      <c r="C154" t="s">
+        <v>339</v>
+      </c>
+      <c r="D154" t="s">
+        <v>203</v>
+      </c>
+      <c r="E154" t="s">
+        <v>923</v>
+      </c>
+      <c r="F154" t="s">
+        <v>868</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>922</v>
+      </c>
+      <c r="B155" t="s">
+        <v>866</v>
+      </c>
+      <c r="C155" t="s">
+        <v>367</v>
+      </c>
+      <c r="D155" t="s">
+        <v>203</v>
+      </c>
+      <c r="E155" t="s">
+        <v>923</v>
+      </c>
+      <c r="F155" t="s">
+        <v>868</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>922</v>
+      </c>
+      <c r="B156" t="s">
+        <v>866</v>
+      </c>
+      <c r="C156" t="s">
+        <v>852</v>
+      </c>
+      <c r="D156" t="s">
+        <v>203</v>
+      </c>
+      <c r="E156" t="s">
+        <v>923</v>
+      </c>
+      <c r="F156" t="s">
+        <v>868</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>927</v>
+      </c>
+      <c r="B157" t="s">
+        <v>399</v>
+      </c>
+      <c r="C157" t="s">
+        <v>400</v>
+      </c>
+      <c r="D157" t="s">
+        <v>203</v>
+      </c>
+      <c r="E157" t="s">
+        <v>928</v>
+      </c>
+      <c r="F157" t="s">
+        <v>402</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>930</v>
+      </c>
+      <c r="B158" t="s">
+        <v>931</v>
+      </c>
+      <c r="C158" t="s">
+        <v>932</v>
+      </c>
+      <c r="D158" t="s">
+        <v>203</v>
+      </c>
+      <c r="E158" t="s">
+        <v>591</v>
+      </c>
+      <c r="F158" t="s">
+        <v>933</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>935</v>
+      </c>
+      <c r="B159" t="s">
+        <v>936</v>
+      </c>
+      <c r="C159" t="s">
+        <v>937</v>
+      </c>
+      <c r="D159" t="s">
+        <v>461</v>
+      </c>
+      <c r="E159" t="s">
+        <v>938</v>
+      </c>
+      <c r="F159" t="s">
+        <v>939</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>941</v>
+      </c>
+      <c r="B160" t="s">
+        <v>942</v>
+      </c>
+      <c r="C160" t="s">
+        <v>943</v>
+      </c>
+      <c r="D160" t="s">
+        <v>203</v>
+      </c>
+      <c r="E160" t="s">
+        <v>944</v>
+      </c>
+      <c r="F160" t="s">
+        <v>945</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>947</v>
+      </c>
+      <c r="B161" t="s">
+        <v>231</v>
+      </c>
+      <c r="C161" t="s">
+        <v>232</v>
+      </c>
+      <c r="D161" t="s">
+        <v>233</v>
+      </c>
+      <c r="E161" t="s">
+        <v>948</v>
+      </c>
+      <c r="F161" t="s">
+        <v>235</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>950</v>
+      </c>
+      <c r="B162" t="s">
+        <v>951</v>
+      </c>
+      <c r="C162" t="s">
+        <v>226</v>
+      </c>
+      <c r="D162" t="s">
+        <v>203</v>
+      </c>
+      <c r="E162" t="s">
+        <v>952</v>
+      </c>
+      <c r="F162" t="s">
+        <v>953</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -3149,6 +7981,135 @@
     <hyperlink ref="H31" r:id="rId30"/>
     <hyperlink ref="H32" r:id="rId31"/>
     <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-17.xlsx
+++ b/docs/xlsx/jobs-2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="961">
   <si>
     <t>Title</t>
   </si>
@@ -1858,6 +1858,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a12806b061ca4e3fab2c657f587d697f-hr-and-compliance-director-education-leadership-foundation-fresno</t>
   </si>
   <si>
+    <t>Human Resources &amp; Payroll Manager</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 7015.00 - 9206.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc2f6c07838b474796c0de62286df619-human-resources-payroll-manager-legal-services-of-northern-california-sacramento</t>
+  </si>
+  <si>
     <t>Human Resources Assistant (Worcester, MA)</t>
   </si>
   <si>
@@ -2069,6 +2081,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3bfb813189984b5cafd6ce5da73dc57f-managing-director-dharmakaya-center-for-wellbeing-cragsmoor</t>
+  </si>
+  <si>
+    <t>Membership Acquisition Lead</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/940f5d60fe4f4a8db0217a3a807d77db-membership-acquisition-lead-american-montessori-society-new-york</t>
   </si>
   <si>
     <t>New England Area Coordinator</t>
@@ -4204,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -6180,171 +6198,171 @@
         <v>614</v>
       </c>
       <c r="B86" t="s">
+        <v>249</v>
+      </c>
+      <c r="C86" t="s">
         <v>615</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>203</v>
+      </c>
+      <c r="E86" t="s">
         <v>616</v>
       </c>
-      <c r="D86" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
+        <v>391</v>
+      </c>
+      <c r="H86" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="F86" t="s">
-        <v>618</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>618</v>
+      </c>
+      <c r="B87" t="s">
+        <v>619</v>
+      </c>
+      <c r="C87" t="s">
         <v>620</v>
       </c>
-      <c r="B87" t="s">
+      <c r="D87" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" t="s">
         <v>621</v>
       </c>
-      <c r="C87" t="s">
+      <c r="F87" t="s">
         <v>622</v>
       </c>
-      <c r="D87" t="s">
-        <v>203</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="H87" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="F87" t="s">
-        <v>624</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>624</v>
+      </c>
+      <c r="B88" t="s">
+        <v>625</v>
+      </c>
+      <c r="C88" t="s">
         <v>626</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
+        <v>203</v>
+      </c>
+      <c r="E88" t="s">
         <v>627</v>
       </c>
-      <c r="C88" t="s">
-        <v>209</v>
-      </c>
-      <c r="D88" t="s">
-        <v>550</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>628</v>
       </c>
-      <c r="F88" t="s">
+      <c r="H88" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>630</v>
+      </c>
+      <c r="B89" t="s">
         <v>631</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" t="s">
+        <v>550</v>
+      </c>
+      <c r="E89" t="s">
         <v>632</v>
       </c>
-      <c r="C89" t="s">
+      <c r="F89" t="s">
         <v>633</v>
       </c>
-      <c r="D89" t="s">
-        <v>203</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="H89" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="F89" t="s">
-        <v>191</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>635</v>
+      </c>
+      <c r="B90" t="s">
         <v>636</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>637</v>
       </c>
-      <c r="C90" t="s">
-        <v>209</v>
-      </c>
       <c r="D90" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E90" t="s">
         <v>638</v>
       </c>
       <c r="F90" t="s">
+        <v>191</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>640</v>
+      </c>
+      <c r="B91" t="s">
         <v>641</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
+        <v>209</v>
+      </c>
+      <c r="D91" t="s">
+        <v>275</v>
+      </c>
+      <c r="E91" t="s">
         <v>642</v>
       </c>
-      <c r="C91" t="s">
+      <c r="F91" t="s">
         <v>643</v>
       </c>
-      <c r="D91" t="s">
-        <v>203</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="H91" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="F91" t="s">
-        <v>645</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B92" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C92" t="s">
-        <v>339</v>
+        <v>647</v>
       </c>
       <c r="D92" t="s">
         <v>203</v>
       </c>
       <c r="E92" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F92" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B93" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C93" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="D93" t="s">
         <v>203</v>
@@ -6353,44 +6371,44 @@
         <v>651</v>
       </c>
       <c r="F93" t="s">
+        <v>649</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>653</v>
+      </c>
+      <c r="B94" t="s">
         <v>654</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" t="s">
+        <v>203</v>
+      </c>
+      <c r="E94" t="s">
         <v>655</v>
       </c>
-      <c r="C94" t="s">
+      <c r="F94" t="s">
         <v>656</v>
       </c>
-      <c r="D94" t="s">
-        <v>203</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="F94" t="s">
-        <v>658</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>658</v>
+      </c>
+      <c r="B95" t="s">
+        <v>659</v>
+      </c>
+      <c r="C95" t="s">
         <v>660</v>
-      </c>
-      <c r="B95" t="s">
-        <v>615</v>
-      </c>
-      <c r="C95" t="s">
-        <v>616</v>
       </c>
       <c r="D95" t="s">
         <v>203</v>
@@ -6399,286 +6417,286 @@
         <v>661</v>
       </c>
       <c r="F95" t="s">
-        <v>191</v>
+        <v>662</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B96" t="s">
-        <v>664</v>
+        <v>619</v>
       </c>
       <c r="C96" t="s">
+        <v>620</v>
+      </c>
+      <c r="D96" t="s">
+        <v>203</v>
+      </c>
+      <c r="E96" t="s">
         <v>665</v>
       </c>
-      <c r="D96" t="s">
-        <v>203</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>191</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="F96" t="s">
-        <v>667</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>667</v>
+      </c>
+      <c r="B97" t="s">
+        <v>668</v>
+      </c>
+      <c r="C97" t="s">
         <v>669</v>
       </c>
-      <c r="B97" t="s">
+      <c r="D97" t="s">
+        <v>203</v>
+      </c>
+      <c r="E97" t="s">
         <v>670</v>
       </c>
-      <c r="C97" t="s">
+      <c r="F97" t="s">
         <v>671</v>
       </c>
-      <c r="D97" t="s">
-        <v>203</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="H97" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="F97" t="s">
-        <v>673</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>673</v>
+      </c>
+      <c r="B98" t="s">
+        <v>674</v>
+      </c>
+      <c r="C98" t="s">
         <v>675</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" t="s">
         <v>676</v>
       </c>
-      <c r="C98" t="s">
-        <v>209</v>
-      </c>
-      <c r="D98" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>677</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>679</v>
+      </c>
+      <c r="B99" t="s">
         <v>680</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>209</v>
+      </c>
+      <c r="D99" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" t="s">
         <v>681</v>
       </c>
-      <c r="C99" t="s">
+      <c r="F99" t="s">
         <v>682</v>
       </c>
-      <c r="D99" t="s">
-        <v>203</v>
-      </c>
-      <c r="E99" t="s">
-        <v>204</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="H99" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100" t="s">
         <v>685</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>686</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" t="s">
+        <v>204</v>
+      </c>
+      <c r="F100" t="s">
         <v>687</v>
       </c>
-      <c r="D100" t="s">
-        <v>275</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="H100" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="F100" t="s">
-        <v>673</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>689</v>
+      </c>
+      <c r="B101" t="s">
+        <v>328</v>
+      </c>
+      <c r="C101" t="s">
+        <v>209</v>
+      </c>
+      <c r="D101" t="s">
+        <v>203</v>
+      </c>
+      <c r="E101" t="s">
+        <v>191</v>
+      </c>
+      <c r="F101" t="s">
+        <v>329</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="B101" t="s">
-        <v>691</v>
-      </c>
-      <c r="C101" t="s">
-        <v>280</v>
-      </c>
-      <c r="D101" t="s">
-        <v>203</v>
-      </c>
-      <c r="E101" t="s">
-        <v>692</v>
-      </c>
-      <c r="F101" t="s">
-        <v>693</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>691</v>
+      </c>
+      <c r="B102" t="s">
+        <v>692</v>
+      </c>
+      <c r="C102" t="s">
+        <v>693</v>
+      </c>
+      <c r="D102" t="s">
+        <v>275</v>
+      </c>
+      <c r="E102" t="s">
+        <v>694</v>
+      </c>
+      <c r="F102" t="s">
+        <v>677</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="B102" t="s">
-        <v>696</v>
-      </c>
-      <c r="C102" t="s">
-        <v>479</v>
-      </c>
-      <c r="D102" t="s">
-        <v>203</v>
-      </c>
-      <c r="E102" t="s">
-        <v>697</v>
-      </c>
-      <c r="F102" t="s">
-        <v>217</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>696</v>
+      </c>
+      <c r="B103" t="s">
+        <v>697</v>
+      </c>
+      <c r="C103" t="s">
+        <v>280</v>
+      </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
+      <c r="E103" t="s">
+        <v>698</v>
+      </c>
+      <c r="F103" t="s">
         <v>699</v>
       </c>
-      <c r="B103" t="s">
+      <c r="H103" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="C103" t="s">
-        <v>339</v>
-      </c>
-      <c r="D103" t="s">
-        <v>203</v>
-      </c>
-      <c r="E103" t="s">
-        <v>701</v>
-      </c>
-      <c r="F103" t="s">
-        <v>702</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>701</v>
+      </c>
+      <c r="B104" t="s">
+        <v>702</v>
+      </c>
+      <c r="C104" t="s">
+        <v>479</v>
+      </c>
+      <c r="D104" t="s">
+        <v>203</v>
+      </c>
+      <c r="E104" t="s">
+        <v>703</v>
+      </c>
+      <c r="F104" t="s">
+        <v>217</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="B104" t="s">
-        <v>705</v>
-      </c>
-      <c r="C104" t="s">
-        <v>706</v>
-      </c>
-      <c r="D104" t="s">
-        <v>461</v>
-      </c>
-      <c r="E104" t="s">
-        <v>707</v>
-      </c>
-      <c r="F104" t="s">
-        <v>708</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B105" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C105" t="s">
-        <v>712</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
         <v>203</v>
       </c>
       <c r="E105" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F105" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="B106" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="C106" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D106" t="s">
-        <v>203</v>
+        <v>461</v>
       </c>
       <c r="E106" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F106" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B107" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C107" t="s">
-        <v>367</v>
+        <v>718</v>
       </c>
       <c r="D107" t="s">
-        <v>461</v>
+        <v>203</v>
       </c>
       <c r="E107" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F107" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -6686,203 +6704,203 @@
         <v>722</v>
       </c>
       <c r="B108" t="s">
-        <v>231</v>
+        <v>723</v>
       </c>
       <c r="C108" t="s">
+        <v>724</v>
+      </c>
+      <c r="D108" t="s">
+        <v>203</v>
+      </c>
+      <c r="E108" t="s">
+        <v>725</v>
+      </c>
+      <c r="F108" t="s">
+        <v>726</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D108" t="s">
-        <v>550</v>
-      </c>
-      <c r="E108" t="s">
-        <v>728</v>
-      </c>
-      <c r="F108" t="s">
-        <v>235</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B109" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C109" t="s">
         <v>367</v>
       </c>
       <c r="D109" t="s">
-        <v>203</v>
+        <v>461</v>
       </c>
       <c r="E109" t="s">
+        <v>730</v>
+      </c>
+      <c r="F109" t="s">
+        <v>731</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="F109" t="s">
-        <v>733</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B110" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" t="s">
+        <v>733</v>
+      </c>
+      <c r="D110" t="s">
+        <v>550</v>
+      </c>
+      <c r="E110" t="s">
+        <v>734</v>
+      </c>
+      <c r="F110" t="s">
+        <v>235</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="C110" t="s">
-        <v>470</v>
-      </c>
-      <c r="D110" t="s">
-        <v>203</v>
-      </c>
-      <c r="E110" t="s">
-        <v>736</v>
-      </c>
-      <c r="F110" t="s">
-        <v>737</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>736</v>
+      </c>
+      <c r="B111" t="s">
+        <v>737</v>
+      </c>
+      <c r="C111" t="s">
+        <v>367</v>
+      </c>
+      <c r="D111" t="s">
+        <v>203</v>
+      </c>
+      <c r="E111" t="s">
+        <v>738</v>
+      </c>
+      <c r="F111" t="s">
         <v>739</v>
       </c>
-      <c r="B111" t="s">
+      <c r="H111" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="C111" t="s">
-        <v>741</v>
-      </c>
-      <c r="D111" t="s">
-        <v>203</v>
-      </c>
-      <c r="E111" t="s">
-        <v>425</v>
-      </c>
-      <c r="F111" t="s">
-        <v>742</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>736</v>
+      </c>
+      <c r="B112" t="s">
+        <v>741</v>
+      </c>
+      <c r="C112" t="s">
+        <v>470</v>
+      </c>
+      <c r="D112" t="s">
+        <v>203</v>
+      </c>
+      <c r="E112" t="s">
+        <v>742</v>
+      </c>
+      <c r="F112" t="s">
+        <v>743</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B112" t="s">
-        <v>745</v>
-      </c>
-      <c r="C112" t="s">
-        <v>746</v>
-      </c>
-      <c r="D112" t="s">
-        <v>275</v>
-      </c>
-      <c r="E112" t="s">
-        <v>747</v>
-      </c>
-      <c r="F112" t="s">
-        <v>748</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B113" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C113" t="s">
-        <v>323</v>
+        <v>747</v>
       </c>
       <c r="D113" t="s">
         <v>203</v>
       </c>
       <c r="E113" t="s">
-        <v>752</v>
+        <v>425</v>
       </c>
       <c r="F113" t="s">
-        <v>673</v>
+        <v>748</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>750</v>
+      </c>
+      <c r="B114" t="s">
+        <v>751</v>
+      </c>
+      <c r="C114" t="s">
+        <v>752</v>
+      </c>
+      <c r="D114" t="s">
+        <v>275</v>
+      </c>
+      <c r="E114" t="s">
+        <v>753</v>
+      </c>
+      <c r="F114" t="s">
         <v>754</v>
       </c>
-      <c r="B114" t="s">
+      <c r="H114" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="C114" t="s">
-        <v>756</v>
-      </c>
-      <c r="D114" t="s">
-        <v>461</v>
-      </c>
-      <c r="E114" t="s">
-        <v>757</v>
-      </c>
-      <c r="F114" t="s">
-        <v>600</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>756</v>
+      </c>
+      <c r="B115" t="s">
+        <v>757</v>
+      </c>
+      <c r="C115" t="s">
+        <v>323</v>
+      </c>
+      <c r="D115" t="s">
+        <v>203</v>
+      </c>
+      <c r="E115" t="s">
+        <v>758</v>
+      </c>
+      <c r="F115" t="s">
+        <v>677</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="B115" t="s">
-        <v>548</v>
-      </c>
-      <c r="C115" t="s">
-        <v>549</v>
-      </c>
-      <c r="D115" t="s">
-        <v>550</v>
-      </c>
-      <c r="E115" t="s">
-        <v>551</v>
-      </c>
-      <c r="F115" t="s">
-        <v>552</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>760</v>
+      </c>
+      <c r="B116" t="s">
         <v>761</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>762</v>
       </c>
-      <c r="C116" t="s">
-        <v>367</v>
-      </c>
       <c r="D116" t="s">
-        <v>203</v>
+        <v>461</v>
       </c>
       <c r="E116" t="s">
         <v>763</v>
       </c>
       <c r="F116" t="s">
-        <v>228</v>
+        <v>600</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>764</v>
@@ -6893,19 +6911,19 @@
         <v>765</v>
       </c>
       <c r="B117" t="s">
-        <v>360</v>
+        <v>548</v>
       </c>
       <c r="C117" t="s">
-        <v>361</v>
+        <v>549</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>550</v>
       </c>
       <c r="E117" t="s">
-        <v>713</v>
+        <v>551</v>
       </c>
       <c r="F117" t="s">
-        <v>363</v>
+        <v>552</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>766</v>
@@ -6919,16 +6937,16 @@
         <v>768</v>
       </c>
       <c r="C118" t="s">
-        <v>209</v>
+        <v>367</v>
       </c>
       <c r="D118" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>539</v>
+        <v>769</v>
       </c>
       <c r="F118" t="s">
-        <v>769</v>
+        <v>228</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>770</v>
@@ -6939,479 +6957,479 @@
         <v>771</v>
       </c>
       <c r="B119" t="s">
+        <v>360</v>
+      </c>
+      <c r="C119" t="s">
+        <v>361</v>
+      </c>
+      <c r="D119" t="s">
+        <v>203</v>
+      </c>
+      <c r="E119" t="s">
+        <v>719</v>
+      </c>
+      <c r="F119" t="s">
+        <v>363</v>
+      </c>
+      <c r="H119" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="C119" t="s">
-        <v>479</v>
-      </c>
-      <c r="D119" t="s">
-        <v>203</v>
-      </c>
-      <c r="E119" t="s">
-        <v>773</v>
-      </c>
-      <c r="F119" t="s">
-        <v>774</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>773</v>
+      </c>
+      <c r="B120" t="s">
+        <v>774</v>
+      </c>
+      <c r="C120" t="s">
+        <v>209</v>
+      </c>
+      <c r="D120" t="s">
+        <v>275</v>
+      </c>
+      <c r="E120" t="s">
+        <v>539</v>
+      </c>
+      <c r="F120" t="s">
+        <v>775</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="B120" t="s">
-        <v>777</v>
-      </c>
-      <c r="C120" t="s">
-        <v>778</v>
-      </c>
-      <c r="D120" t="s">
-        <v>203</v>
-      </c>
-      <c r="E120" t="s">
-        <v>617</v>
-      </c>
-      <c r="F120" t="s">
-        <v>779</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>777</v>
+      </c>
+      <c r="B121" t="s">
+        <v>778</v>
+      </c>
+      <c r="C121" t="s">
+        <v>479</v>
+      </c>
+      <c r="D121" t="s">
+        <v>203</v>
+      </c>
+      <c r="E121" t="s">
+        <v>779</v>
+      </c>
+      <c r="F121" t="s">
+        <v>780</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="B121" t="s">
-        <v>782</v>
-      </c>
-      <c r="C121" t="s">
-        <v>339</v>
-      </c>
-      <c r="D121" t="s">
-        <v>275</v>
-      </c>
-      <c r="E121" t="s">
-        <v>191</v>
-      </c>
-      <c r="F121" t="s">
-        <v>205</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>782</v>
+      </c>
+      <c r="B122" t="s">
+        <v>783</v>
+      </c>
+      <c r="C122" t="s">
         <v>784</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>203</v>
+      </c>
+      <c r="E122" t="s">
+        <v>621</v>
+      </c>
+      <c r="F122" t="s">
         <v>785</v>
       </c>
-      <c r="C122" t="s">
-        <v>202</v>
-      </c>
-      <c r="D122" t="s">
-        <v>203</v>
-      </c>
-      <c r="E122" t="s">
+      <c r="H122" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="F122" t="s">
-        <v>787</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>787</v>
+      </c>
+      <c r="B123" t="s">
+        <v>788</v>
+      </c>
+      <c r="C123" t="s">
+        <v>339</v>
+      </c>
+      <c r="D123" t="s">
+        <v>275</v>
+      </c>
+      <c r="E123" t="s">
+        <v>191</v>
+      </c>
+      <c r="F123" t="s">
+        <v>205</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="B123" t="s">
-        <v>790</v>
-      </c>
-      <c r="C123" t="s">
-        <v>221</v>
-      </c>
-      <c r="D123" t="s">
-        <v>203</v>
-      </c>
-      <c r="E123" t="s">
-        <v>791</v>
-      </c>
-      <c r="F123" t="s">
-        <v>792</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>790</v>
+      </c>
+      <c r="B124" t="s">
+        <v>791</v>
+      </c>
+      <c r="C124" t="s">
+        <v>202</v>
+      </c>
+      <c r="D124" t="s">
+        <v>203</v>
+      </c>
+      <c r="E124" t="s">
+        <v>792</v>
+      </c>
+      <c r="F124" t="s">
+        <v>793</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B124" t="s">
-        <v>394</v>
-      </c>
-      <c r="C124" t="s">
-        <v>395</v>
-      </c>
-      <c r="D124" t="s">
-        <v>203</v>
-      </c>
-      <c r="E124" t="s">
-        <v>191</v>
-      </c>
-      <c r="F124" t="s">
-        <v>396</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>194</v>
+        <v>795</v>
       </c>
       <c r="B125" t="s">
         <v>796</v>
       </c>
       <c r="C125" t="s">
+        <v>221</v>
+      </c>
+      <c r="D125" t="s">
+        <v>203</v>
+      </c>
+      <c r="E125" t="s">
         <v>797</v>
       </c>
-      <c r="D125" t="s">
-        <v>203</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>798</v>
       </c>
-      <c r="F125" t="s">
+      <c r="H125" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>800</v>
+      </c>
+      <c r="B126" t="s">
+        <v>394</v>
+      </c>
+      <c r="C126" t="s">
+        <v>395</v>
+      </c>
+      <c r="D126" t="s">
+        <v>203</v>
+      </c>
+      <c r="E126" t="s">
+        <v>191</v>
+      </c>
+      <c r="F126" t="s">
+        <v>396</v>
+      </c>
+      <c r="H126" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="B126" t="s">
-        <v>802</v>
-      </c>
-      <c r="C126" t="s">
-        <v>803</v>
-      </c>
-      <c r="D126" t="s">
-        <v>203</v>
-      </c>
-      <c r="E126" t="s">
-        <v>436</v>
-      </c>
-      <c r="F126" t="s">
-        <v>329</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>194</v>
+      </c>
+      <c r="B127" t="s">
+        <v>802</v>
+      </c>
+      <c r="C127" t="s">
+        <v>803</v>
+      </c>
+      <c r="D127" t="s">
+        <v>203</v>
+      </c>
+      <c r="E127" t="s">
+        <v>804</v>
+      </c>
+      <c r="F127" t="s">
         <v>805</v>
       </c>
-      <c r="B127" t="s">
+      <c r="H127" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C127" t="s">
-        <v>209</v>
-      </c>
-      <c r="D127" t="s">
-        <v>203</v>
-      </c>
-      <c r="E127" t="s">
-        <v>807</v>
-      </c>
-      <c r="F127" t="s">
-        <v>191</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>807</v>
+      </c>
+      <c r="B128" t="s">
+        <v>808</v>
+      </c>
+      <c r="C128" t="s">
         <v>809</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
+        <v>203</v>
+      </c>
+      <c r="E128" t="s">
+        <v>436</v>
+      </c>
+      <c r="F128" t="s">
+        <v>329</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="C128" t="s">
-        <v>221</v>
-      </c>
-      <c r="D128" t="s">
-        <v>203</v>
-      </c>
-      <c r="E128" t="s">
-        <v>811</v>
-      </c>
-      <c r="F128" t="s">
-        <v>812</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>811</v>
+      </c>
+      <c r="B129" t="s">
+        <v>812</v>
+      </c>
+      <c r="C129" t="s">
+        <v>209</v>
+      </c>
+      <c r="D129" t="s">
+        <v>203</v>
+      </c>
+      <c r="E129" t="s">
+        <v>813</v>
+      </c>
+      <c r="F129" t="s">
+        <v>191</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="B129" t="s">
-        <v>815</v>
-      </c>
-      <c r="C129" t="s">
-        <v>202</v>
-      </c>
-      <c r="D129" t="s">
-        <v>461</v>
-      </c>
-      <c r="E129" t="s">
-        <v>816</v>
-      </c>
-      <c r="F129" t="s">
-        <v>563</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>815</v>
+      </c>
+      <c r="B130" t="s">
+        <v>816</v>
+      </c>
+      <c r="C130" t="s">
+        <v>221</v>
+      </c>
+      <c r="D130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E130" t="s">
+        <v>817</v>
+      </c>
+      <c r="F130" t="s">
         <v>818</v>
       </c>
-      <c r="B130" t="s">
+      <c r="H130" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="C130" t="s">
-        <v>820</v>
-      </c>
-      <c r="D130" t="s">
-        <v>203</v>
-      </c>
-      <c r="E130" t="s">
-        <v>821</v>
-      </c>
-      <c r="F130" t="s">
-        <v>391</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>820</v>
+      </c>
+      <c r="B131" t="s">
+        <v>821</v>
+      </c>
+      <c r="C131" t="s">
+        <v>202</v>
+      </c>
+      <c r="D131" t="s">
+        <v>461</v>
+      </c>
+      <c r="E131" t="s">
+        <v>822</v>
+      </c>
+      <c r="F131" t="s">
+        <v>563</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="B131" t="s">
-        <v>824</v>
-      </c>
-      <c r="C131" t="s">
-        <v>262</v>
-      </c>
-      <c r="D131" t="s">
-        <v>203</v>
-      </c>
-      <c r="E131" t="s">
-        <v>825</v>
-      </c>
-      <c r="F131" t="s">
-        <v>826</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B132" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C132" t="s">
+        <v>826</v>
+      </c>
+      <c r="D132" t="s">
+        <v>203</v>
+      </c>
+      <c r="E132" t="s">
+        <v>827</v>
+      </c>
+      <c r="F132" t="s">
+        <v>391</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="D132" t="s">
-        <v>203</v>
-      </c>
-      <c r="E132" t="s">
-        <v>825</v>
-      </c>
-      <c r="F132" t="s">
-        <v>826</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>829</v>
+      </c>
+      <c r="B133" t="s">
         <v>830</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
+        <v>262</v>
+      </c>
+      <c r="D133" t="s">
+        <v>203</v>
+      </c>
+      <c r="E133" t="s">
         <v>831</v>
       </c>
-      <c r="C133" t="s">
+      <c r="F133" t="s">
         <v>832</v>
       </c>
-      <c r="D133" t="s">
-        <v>203</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="H133" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="F133" t="s">
-        <v>834</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="B134" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="C134" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="D134" t="s">
-        <v>461</v>
+        <v>203</v>
       </c>
       <c r="E134" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="F134" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="B135" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="C135" t="s">
-        <v>209</v>
+        <v>838</v>
       </c>
       <c r="D135" t="s">
         <v>203</v>
       </c>
       <c r="E135" t="s">
-        <v>713</v>
+        <v>839</v>
       </c>
       <c r="F135" t="s">
-        <v>329</v>
+        <v>840</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>842</v>
+      </c>
+      <c r="B136" t="s">
+        <v>843</v>
+      </c>
+      <c r="C136" t="s">
+        <v>844</v>
+      </c>
+      <c r="D136" t="s">
+        <v>461</v>
+      </c>
+      <c r="E136" t="s">
         <v>845</v>
       </c>
-      <c r="B136" t="s">
+      <c r="F136" t="s">
         <v>846</v>
       </c>
-      <c r="C136" t="s">
-        <v>209</v>
-      </c>
-      <c r="D136" t="s">
-        <v>203</v>
-      </c>
-      <c r="E136" t="s">
+      <c r="H136" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="F136" t="s">
-        <v>848</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B137" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C137" t="s">
-        <v>852</v>
+        <v>209</v>
       </c>
       <c r="D137" t="s">
         <v>203</v>
       </c>
       <c r="E137" t="s">
-        <v>853</v>
+        <v>719</v>
       </c>
       <c r="F137" t="s">
         <v>329</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>851</v>
+      </c>
+      <c r="B138" t="s">
+        <v>852</v>
+      </c>
+      <c r="C138" t="s">
+        <v>209</v>
+      </c>
+      <c r="D138" t="s">
+        <v>203</v>
+      </c>
+      <c r="E138" t="s">
+        <v>853</v>
+      </c>
+      <c r="F138" t="s">
+        <v>854</v>
+      </c>
+      <c r="H138" s="2" t="s">
         <v>855</v>
-      </c>
-      <c r="B138" t="s">
-        <v>609</v>
-      </c>
-      <c r="C138" t="s">
-        <v>610</v>
-      </c>
-      <c r="D138" t="s">
-        <v>203</v>
-      </c>
-      <c r="E138" t="s">
-        <v>856</v>
-      </c>
-      <c r="F138" t="s">
-        <v>629</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B139" t="s">
+        <v>857</v>
+      </c>
+      <c r="C139" t="s">
         <v>858</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
+        <v>203</v>
+      </c>
+      <c r="E139" t="s">
         <v>859</v>
       </c>
-      <c r="D139" t="s">
-        <v>203</v>
-      </c>
-      <c r="E139" t="s">
-        <v>191</v>
-      </c>
       <c r="F139" t="s">
-        <v>391</v>
+        <v>329</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>860</v>
@@ -7419,13 +7437,13 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="B140" t="s">
-        <v>861</v>
+        <v>609</v>
       </c>
       <c r="C140" t="s">
-        <v>209</v>
+        <v>610</v>
       </c>
       <c r="D140" t="s">
         <v>203</v>
@@ -7434,191 +7452,191 @@
         <v>862</v>
       </c>
       <c r="F140" t="s">
+        <v>633</v>
+      </c>
+      <c r="H140" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>861</v>
+      </c>
+      <c r="B141" t="s">
+        <v>864</v>
+      </c>
+      <c r="C141" t="s">
         <v>865</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D141" t="s">
+        <v>203</v>
+      </c>
+      <c r="E141" t="s">
+        <v>191</v>
+      </c>
+      <c r="F141" t="s">
+        <v>391</v>
+      </c>
+      <c r="H141" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="C141" t="s">
-        <v>852</v>
-      </c>
-      <c r="D141" t="s">
-        <v>203</v>
-      </c>
-      <c r="E141" t="s">
-        <v>867</v>
-      </c>
-      <c r="F141" t="s">
-        <v>868</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>861</v>
+      </c>
+      <c r="B142" t="s">
+        <v>867</v>
+      </c>
+      <c r="C142" t="s">
+        <v>209</v>
+      </c>
+      <c r="D142" t="s">
+        <v>203</v>
+      </c>
+      <c r="E142" t="s">
+        <v>868</v>
+      </c>
+      <c r="F142" t="s">
+        <v>869</v>
+      </c>
+      <c r="H142" s="2" t="s">
         <v>870</v>
-      </c>
-      <c r="B142" t="s">
-        <v>866</v>
-      </c>
-      <c r="C142" t="s">
-        <v>367</v>
-      </c>
-      <c r="D142" t="s">
-        <v>203</v>
-      </c>
-      <c r="E142" t="s">
-        <v>867</v>
-      </c>
-      <c r="F142" t="s">
-        <v>868</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>871</v>
+      </c>
+      <c r="B143" t="s">
         <v>872</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
+        <v>858</v>
+      </c>
+      <c r="D143" t="s">
+        <v>203</v>
+      </c>
+      <c r="E143" t="s">
         <v>873</v>
       </c>
-      <c r="C143" t="s">
-        <v>367</v>
-      </c>
-      <c r="D143" t="s">
-        <v>203</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>874</v>
       </c>
-      <c r="F143" t="s">
+      <c r="H143" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>876</v>
+      </c>
+      <c r="B144" t="s">
+        <v>872</v>
+      </c>
+      <c r="C144" t="s">
+        <v>367</v>
+      </c>
+      <c r="D144" t="s">
+        <v>203</v>
+      </c>
+      <c r="E144" t="s">
+        <v>873</v>
+      </c>
+      <c r="F144" t="s">
+        <v>874</v>
+      </c>
+      <c r="H144" s="2" t="s">
         <v>877</v>
-      </c>
-      <c r="B144" t="s">
-        <v>878</v>
-      </c>
-      <c r="C144" t="s">
-        <v>879</v>
-      </c>
-      <c r="D144" t="s">
-        <v>203</v>
-      </c>
-      <c r="E144" t="s">
-        <v>880</v>
-      </c>
-      <c r="F144" t="s">
-        <v>881</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="B145" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C145" t="s">
-        <v>885</v>
+        <v>367</v>
       </c>
       <c r="D145" t="s">
         <v>203</v>
       </c>
       <c r="E145" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="F145" t="s">
-        <v>191</v>
+        <v>881</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>883</v>
+      </c>
+      <c r="B146" t="s">
+        <v>884</v>
+      </c>
+      <c r="C146" t="s">
+        <v>885</v>
+      </c>
+      <c r="D146" t="s">
+        <v>203</v>
+      </c>
+      <c r="E146" t="s">
+        <v>886</v>
+      </c>
+      <c r="F146" t="s">
+        <v>887</v>
+      </c>
+      <c r="H146" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="B146" t="s">
-        <v>851</v>
-      </c>
-      <c r="C146" t="s">
-        <v>852</v>
-      </c>
-      <c r="D146" t="s">
-        <v>550</v>
-      </c>
-      <c r="E146" t="s">
-        <v>889</v>
-      </c>
-      <c r="F146" t="s">
-        <v>329</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>889</v>
+      </c>
+      <c r="B147" t="s">
+        <v>890</v>
+      </c>
+      <c r="C147" t="s">
         <v>891</v>
       </c>
-      <c r="B147" t="s">
-        <v>615</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
+        <v>203</v>
+      </c>
+      <c r="E147" t="s">
         <v>892</v>
-      </c>
-      <c r="D147" t="s">
-        <v>550</v>
-      </c>
-      <c r="E147" t="s">
-        <v>893</v>
       </c>
       <c r="F147" t="s">
         <v>191</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>894</v>
+      </c>
+      <c r="B148" t="s">
+        <v>857</v>
+      </c>
+      <c r="C148" t="s">
+        <v>858</v>
+      </c>
+      <c r="D148" t="s">
+        <v>550</v>
+      </c>
+      <c r="E148" t="s">
         <v>895</v>
       </c>
-      <c r="B148" t="s">
-        <v>399</v>
-      </c>
-      <c r="C148" t="s">
-        <v>400</v>
-      </c>
-      <c r="D148" t="s">
-        <v>233</v>
-      </c>
-      <c r="E148" t="s">
-        <v>191</v>
-      </c>
       <c r="F148" t="s">
-        <v>191</v>
+        <v>329</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>896</v>
@@ -7629,137 +7647,137 @@
         <v>897</v>
       </c>
       <c r="B149" t="s">
+        <v>619</v>
+      </c>
+      <c r="C149" t="s">
         <v>898</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
+        <v>550</v>
+      </c>
+      <c r="E149" t="s">
         <v>899</v>
-      </c>
-      <c r="D149" t="s">
-        <v>203</v>
-      </c>
-      <c r="E149" t="s">
-        <v>900</v>
       </c>
       <c r="F149" t="s">
         <v>191</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>901</v>
+      </c>
+      <c r="B150" t="s">
+        <v>399</v>
+      </c>
+      <c r="C150" t="s">
+        <v>400</v>
+      </c>
+      <c r="D150" t="s">
+        <v>233</v>
+      </c>
+      <c r="E150" t="s">
+        <v>191</v>
+      </c>
+      <c r="F150" t="s">
+        <v>191</v>
+      </c>
+      <c r="H150" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="B150" t="s">
-        <v>903</v>
-      </c>
-      <c r="C150" t="s">
-        <v>226</v>
-      </c>
-      <c r="D150" t="s">
-        <v>203</v>
-      </c>
-      <c r="E150" t="s">
-        <v>904</v>
-      </c>
-      <c r="F150" t="s">
-        <v>905</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B151" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C151" t="s">
-        <v>367</v>
+        <v>905</v>
       </c>
       <c r="D151" t="s">
         <v>203</v>
       </c>
       <c r="E151" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F151" t="s">
         <v>191</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>908</v>
+      </c>
+      <c r="B152" t="s">
+        <v>909</v>
+      </c>
+      <c r="C152" t="s">
+        <v>226</v>
+      </c>
+      <c r="D152" t="s">
+        <v>203</v>
+      </c>
+      <c r="E152" t="s">
+        <v>910</v>
+      </c>
+      <c r="F152" t="s">
         <v>911</v>
       </c>
-      <c r="B152" t="s">
+      <c r="H152" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="C152" t="s">
-        <v>913</v>
-      </c>
-      <c r="D152" t="s">
-        <v>203</v>
-      </c>
-      <c r="E152" t="s">
-        <v>914</v>
-      </c>
-      <c r="F152" t="s">
-        <v>205</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>913</v>
+      </c>
+      <c r="B153" t="s">
+        <v>914</v>
+      </c>
+      <c r="C153" t="s">
+        <v>367</v>
+      </c>
+      <c r="D153" t="s">
+        <v>203</v>
+      </c>
+      <c r="E153" t="s">
+        <v>915</v>
+      </c>
+      <c r="F153" t="s">
+        <v>191</v>
+      </c>
+      <c r="H153" s="2" t="s">
         <v>916</v>
-      </c>
-      <c r="B153" t="s">
-        <v>917</v>
-      </c>
-      <c r="C153" t="s">
-        <v>918</v>
-      </c>
-      <c r="D153" t="s">
-        <v>203</v>
-      </c>
-      <c r="E153" t="s">
-        <v>919</v>
-      </c>
-      <c r="F153" t="s">
-        <v>920</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B154" t="s">
-        <v>866</v>
+        <v>918</v>
       </c>
       <c r="C154" t="s">
-        <v>339</v>
+        <v>919</v>
       </c>
       <c r="D154" t="s">
         <v>203</v>
       </c>
       <c r="E154" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="F154" t="s">
-        <v>868</v>
+        <v>205</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -7767,183 +7785,229 @@
         <v>922</v>
       </c>
       <c r="B155" t="s">
-        <v>866</v>
+        <v>923</v>
       </c>
       <c r="C155" t="s">
-        <v>367</v>
+        <v>924</v>
       </c>
       <c r="D155" t="s">
         <v>203</v>
       </c>
       <c r="E155" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="F155" t="s">
-        <v>868</v>
+        <v>926</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B156" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C156" t="s">
-        <v>852</v>
+        <v>339</v>
       </c>
       <c r="D156" t="s">
         <v>203</v>
       </c>
       <c r="E156" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="F156" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B157" t="s">
-        <v>399</v>
+        <v>872</v>
       </c>
       <c r="C157" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="D157" t="s">
         <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F157" t="s">
-        <v>402</v>
+        <v>874</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B158" t="s">
-        <v>931</v>
+        <v>872</v>
       </c>
       <c r="C158" t="s">
+        <v>858</v>
+      </c>
+      <c r="D158" t="s">
+        <v>203</v>
+      </c>
+      <c r="E158" t="s">
+        <v>929</v>
+      </c>
+      <c r="F158" t="s">
+        <v>874</v>
+      </c>
+      <c r="H158" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="D158" t="s">
-        <v>203</v>
-      </c>
-      <c r="E158" t="s">
-        <v>591</v>
-      </c>
-      <c r="F158" t="s">
-        <v>933</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>933</v>
+      </c>
+      <c r="B159" t="s">
+        <v>399</v>
+      </c>
+      <c r="C159" t="s">
+        <v>400</v>
+      </c>
+      <c r="D159" t="s">
+        <v>203</v>
+      </c>
+      <c r="E159" t="s">
+        <v>934</v>
+      </c>
+      <c r="F159" t="s">
+        <v>402</v>
+      </c>
+      <c r="H159" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="B159" t="s">
-        <v>936</v>
-      </c>
-      <c r="C159" t="s">
-        <v>937</v>
-      </c>
-      <c r="D159" t="s">
-        <v>461</v>
-      </c>
-      <c r="E159" t="s">
-        <v>938</v>
-      </c>
-      <c r="F159" t="s">
-        <v>939</v>
-      </c>
-      <c r="H159" s="2" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B160" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="C160" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="D160" t="s">
         <v>203</v>
       </c>
       <c r="E160" t="s">
-        <v>944</v>
+        <v>591</v>
       </c>
       <c r="F160" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="B161" t="s">
-        <v>231</v>
+        <v>942</v>
       </c>
       <c r="C161" t="s">
-        <v>232</v>
+        <v>943</v>
       </c>
       <c r="D161" t="s">
-        <v>233</v>
+        <v>461</v>
       </c>
       <c r="E161" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="F161" t="s">
-        <v>235</v>
+        <v>945</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>947</v>
+      </c>
+      <c r="B162" t="s">
+        <v>948</v>
+      </c>
+      <c r="C162" t="s">
+        <v>949</v>
+      </c>
+      <c r="D162" t="s">
+        <v>203</v>
+      </c>
+      <c r="E162" t="s">
         <v>950</v>
       </c>
-      <c r="B162" t="s">
+      <c r="F162" t="s">
         <v>951</v>
       </c>
-      <c r="C162" t="s">
+      <c r="H162" s="2" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>953</v>
+      </c>
+      <c r="B163" t="s">
+        <v>231</v>
+      </c>
+      <c r="C163" t="s">
+        <v>232</v>
+      </c>
+      <c r="D163" t="s">
+        <v>233</v>
+      </c>
+      <c r="E163" t="s">
+        <v>954</v>
+      </c>
+      <c r="F163" t="s">
+        <v>235</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>956</v>
+      </c>
+      <c r="B164" t="s">
+        <v>957</v>
+      </c>
+      <c r="C164" t="s">
         <v>226</v>
       </c>
-      <c r="D162" t="s">
-        <v>203</v>
-      </c>
-      <c r="E162" t="s">
-        <v>952</v>
-      </c>
-      <c r="F162" t="s">
-        <v>953</v>
-      </c>
-      <c r="H162" s="2" t="s">
-        <v>954</v>
+      <c r="D164" t="s">
+        <v>203</v>
+      </c>
+      <c r="E164" t="s">
+        <v>958</v>
+      </c>
+      <c r="F164" t="s">
+        <v>959</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -8110,6 +8174,8 @@
     <hyperlink ref="H160" r:id="rId159"/>
     <hyperlink ref="H161" r:id="rId160"/>
     <hyperlink ref="H162" r:id="rId161"/>
+    <hyperlink ref="H163" r:id="rId162"/>
+    <hyperlink ref="H164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-17.xlsx
+++ b/docs/xlsx/jobs-2026-08-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="964">
   <si>
     <t>Title</t>
   </si>
@@ -1255,6 +1255,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/11388e5f7f364888a492e2829104358f-detainee-rights-project-lead-the-immigrant-law-center-of-minnesota-saint-paul</t>
   </si>
   <si>
+    <t>Development &amp; Individual Giving Coordinator – Part-Time</t>
+  </si>
+  <si>
+    <t>LEAP Self-Defense</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d2b69cfc69e46eb88025ef397c7a43f-development-individual-giving-coordinator-part-time-leap-self-defense-boston</t>
+  </si>
+  <si>
     <t>Development Associate, Data and Operations</t>
   </si>
   <si>
@@ -1399,9 +1417,6 @@
     <t>Remote (Denver, Colorado)</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 25.00 - 35.00/hour</t>
   </si>
   <si>
@@ -1705,9 +1720,6 @@
     <t>OPEN BOOKS</t>
   </si>
   <si>
-    <t>Community Development, Education, Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d8c753ca090140c59324d27c37f713eb-executive-director-open-books-chicago</t>
   </si>
   <si>
@@ -2477,9 +2489,6 @@
   </si>
   <si>
     <t>Senior Individual Giving Officer / Major Gifts Officer (Part-Time)</t>
-  </si>
-  <si>
-    <t>LEAP Self-Defense</t>
   </si>
   <si>
     <t>USD 35.00 - 45.00/hour</t>
@@ -4222,7 +4231,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5169,96 +5178,96 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>203</v>
+        <v>415</v>
       </c>
       <c r="E41" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F41" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C42" t="s">
-        <v>367</v>
+        <v>202</v>
       </c>
       <c r="D42" t="s">
         <v>203</v>
       </c>
       <c r="E42" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F42" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>367</v>
       </c>
       <c r="D43" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F43" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E44" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F44" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C45" t="s">
-        <v>435</v>
+        <v>226</v>
       </c>
       <c r="D45" t="s">
         <v>203</v>
@@ -5281,125 +5290,125 @@
         <v>440</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>441</v>
       </c>
       <c r="D46" t="s">
         <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F46" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>446</v>
       </c>
       <c r="C47" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="D47" t="s">
         <v>203</v>
       </c>
       <c r="E47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F47" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s">
-        <v>449</v>
+        <v>243</v>
       </c>
       <c r="C48" t="s">
-        <v>450</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
         <v>203</v>
       </c>
       <c r="E48" t="s">
-        <v>210</v>
+        <v>451</v>
       </c>
       <c r="F48" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>456</v>
       </c>
       <c r="D49" t="s">
         <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>455</v>
+        <v>210</v>
       </c>
       <c r="F49" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C50" t="s">
-        <v>460</v>
+        <v>209</v>
       </c>
       <c r="D50" t="s">
+        <v>203</v>
+      </c>
+      <c r="E50" t="s">
         <v>461</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>462</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>464</v>
+      </c>
+      <c r="B51" t="s">
         <v>465</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>466</v>
       </c>
-      <c r="C51" t="s">
-        <v>209</v>
-      </c>
       <c r="D51" t="s">
-        <v>203</v>
+        <v>415</v>
       </c>
       <c r="E51" t="s">
         <v>467</v>
@@ -5413,45 +5422,45 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C52" t="s">
-        <v>470</v>
+        <v>209</v>
       </c>
       <c r="D52" t="s">
         <v>203</v>
       </c>
       <c r="E52" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F52" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>470</v>
+      </c>
+      <c r="B53" t="s">
+        <v>471</v>
+      </c>
+      <c r="C53" t="s">
+        <v>475</v>
+      </c>
+      <c r="D53" t="s">
+        <v>203</v>
+      </c>
+      <c r="E53" t="s">
         <v>472</v>
       </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
         <v>473</v>
-      </c>
-      <c r="C53" t="s">
-        <v>339</v>
-      </c>
-      <c r="D53" t="s">
-        <v>203</v>
-      </c>
-      <c r="E53" t="s">
-        <v>474</v>
-      </c>
-      <c r="F53" t="s">
-        <v>475</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>476</v>
@@ -5465,50 +5474,50 @@
         <v>478</v>
       </c>
       <c r="C54" t="s">
+        <v>339</v>
+      </c>
+      <c r="D54" t="s">
+        <v>203</v>
+      </c>
+      <c r="E54" t="s">
         <v>479</v>
       </c>
-      <c r="D54" t="s">
-        <v>203</v>
-      </c>
-      <c r="E54" t="s">
-        <v>191</v>
-      </c>
       <c r="F54" t="s">
-        <v>191</v>
+        <v>480</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="C55" t="s">
-        <v>209</v>
+        <v>484</v>
       </c>
       <c r="D55" t="s">
         <v>203</v>
       </c>
       <c r="E55" t="s">
-        <v>482</v>
+        <v>191</v>
       </c>
       <c r="F55" t="s">
-        <v>442</v>
+        <v>191</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="C56" t="s">
         <v>209</v>
@@ -5517,10 +5526,10 @@
         <v>203</v>
       </c>
       <c r="E56" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F56" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>488</v>
@@ -5534,168 +5543,168 @@
         <v>490</v>
       </c>
       <c r="C57" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" t="s">
+        <v>203</v>
+      </c>
+      <c r="E57" t="s">
         <v>491</v>
       </c>
-      <c r="D57" t="s">
-        <v>203</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>492</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>494</v>
+      </c>
+      <c r="B58" t="s">
         <v>495</v>
       </c>
-      <c r="B58" t="s">
-        <v>399</v>
-      </c>
       <c r="C58" t="s">
-        <v>400</v>
+        <v>496</v>
       </c>
       <c r="D58" t="s">
         <v>203</v>
       </c>
       <c r="E58" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F58" t="s">
-        <v>191</v>
+        <v>498</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B59" t="s">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="C59" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="D59" t="s">
-        <v>461</v>
+        <v>203</v>
       </c>
       <c r="E59" t="s">
+        <v>501</v>
+      </c>
+      <c r="F59" t="s">
         <v>191</v>
       </c>
-      <c r="F59" t="s">
-        <v>500</v>
-      </c>
       <c r="H59" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="C60" t="s">
-        <v>460</v>
+        <v>367</v>
       </c>
       <c r="D60" t="s">
-        <v>461</v>
+        <v>415</v>
       </c>
       <c r="E60" t="s">
-        <v>503</v>
+        <v>191</v>
       </c>
       <c r="F60" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B61" t="s">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="C61" t="s">
-        <v>339</v>
+        <v>466</v>
       </c>
       <c r="D61" t="s">
-        <v>203</v>
+        <v>415</v>
       </c>
       <c r="E61" t="s">
-        <v>425</v>
+        <v>508</v>
       </c>
       <c r="F61" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B62" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C62" t="s">
-        <v>511</v>
+        <v>339</v>
       </c>
       <c r="D62" t="s">
         <v>203</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>431</v>
       </c>
       <c r="F62" t="s">
-        <v>191</v>
+        <v>512</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C63" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D63" t="s">
         <v>203</v>
       </c>
       <c r="E63" t="s">
-        <v>516</v>
+        <v>191</v>
       </c>
       <c r="F63" t="s">
+        <v>191</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>518</v>
+      </c>
+      <c r="B64" t="s">
         <v>519</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>520</v>
-      </c>
-      <c r="C64" t="s">
-        <v>209</v>
       </c>
       <c r="D64" t="s">
         <v>203</v>
@@ -5741,7 +5750,7 @@
         <v>530</v>
       </c>
       <c r="C66" t="s">
-        <v>367</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
         <v>203</v>
@@ -5773,93 +5782,93 @@
         <v>536</v>
       </c>
       <c r="F67" t="s">
-        <v>191</v>
+        <v>537</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>540</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>367</v>
       </c>
       <c r="D68" t="s">
         <v>203</v>
       </c>
       <c r="E68" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F68" t="s">
-        <v>258</v>
+        <v>191</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B69" t="s">
-        <v>542</v>
+        <v>255</v>
       </c>
       <c r="C69" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E69" t="s">
         <v>544</v>
       </c>
       <c r="F69" t="s">
+        <v>258</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>546</v>
+      </c>
+      <c r="B70" t="s">
         <v>547</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>548</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
+        <v>275</v>
+      </c>
+      <c r="E70" t="s">
         <v>549</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
         <v>550</v>
       </c>
-      <c r="E70" t="s">
+      <c r="H70" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="F70" t="s">
-        <v>552</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>552</v>
+      </c>
+      <c r="B71" t="s">
+        <v>553</v>
+      </c>
+      <c r="C71" t="s">
         <v>554</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>555</v>
-      </c>
-      <c r="C71" t="s">
-        <v>367</v>
-      </c>
-      <c r="D71" t="s">
-        <v>203</v>
       </c>
       <c r="E71" t="s">
         <v>556</v>
@@ -5879,73 +5888,73 @@
         <v>560</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>367</v>
       </c>
       <c r="D72" t="s">
         <v>203</v>
       </c>
       <c r="E72" t="s">
-        <v>204</v>
+        <v>561</v>
       </c>
       <c r="F72" t="s">
-        <v>191</v>
+        <v>562</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>564</v>
       </c>
       <c r="B73" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C73" t="s">
-        <v>339</v>
+        <v>209</v>
       </c>
       <c r="D73" t="s">
         <v>203</v>
       </c>
       <c r="E73" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="F73" t="s">
-        <v>563</v>
+        <v>191</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>565</v>
+        <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="D74" t="s">
         <v>203</v>
       </c>
       <c r="E74" t="s">
-        <v>567</v>
+        <v>293</v>
       </c>
       <c r="F74" t="s">
+        <v>417</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>569</v>
+      </c>
+      <c r="B75" t="s">
         <v>570</v>
-      </c>
-      <c r="B75" t="s">
-        <v>571</v>
       </c>
       <c r="C75" t="s">
         <v>209</v>
@@ -5954,67 +5963,67 @@
         <v>203</v>
       </c>
       <c r="E75" t="s">
+        <v>571</v>
+      </c>
+      <c r="F75" t="s">
         <v>572</v>
       </c>
-      <c r="F75" t="s">
+      <c r="H75" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>574</v>
+      </c>
+      <c r="B76" t="s">
         <v>575</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" t="s">
+        <v>203</v>
+      </c>
+      <c r="E76" t="s">
         <v>576</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" t="s">
         <v>577</v>
       </c>
-      <c r="D76" t="s">
-        <v>461</v>
-      </c>
-      <c r="E76" t="s">
-        <v>539</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="H76" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>579</v>
+      </c>
+      <c r="B77" t="s">
         <v>580</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>581</v>
       </c>
-      <c r="C77" t="s">
-        <v>209</v>
-      </c>
       <c r="D77" t="s">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="E77" t="s">
+        <v>544</v>
+      </c>
+      <c r="F77" t="s">
         <v>582</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B78" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C78" t="s">
         <v>209</v>
@@ -6023,33 +6032,33 @@
         <v>275</v>
       </c>
       <c r="E78" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="F78" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>584</v>
+      </c>
+      <c r="B79" t="s">
+        <v>585</v>
+      </c>
+      <c r="C79" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" t="s">
+        <v>275</v>
+      </c>
+      <c r="E79" t="s">
         <v>586</v>
       </c>
-      <c r="B79" t="s">
+      <c r="F79" t="s">
         <v>587</v>
-      </c>
-      <c r="C79" t="s">
-        <v>221</v>
-      </c>
-      <c r="D79" t="s">
-        <v>203</v>
-      </c>
-      <c r="E79" t="s">
-        <v>588</v>
-      </c>
-      <c r="F79" t="s">
-        <v>191</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>589</v>
@@ -6060,157 +6069,157 @@
         <v>590</v>
       </c>
       <c r="B80" t="s">
-        <v>414</v>
+        <v>591</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="D80" t="s">
         <v>203</v>
       </c>
       <c r="E80" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F80" t="s">
-        <v>416</v>
+        <v>191</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B81" t="s">
-        <v>593</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D81" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E81" t="s">
-        <v>191</v>
+        <v>595</v>
       </c>
       <c r="F81" t="s">
-        <v>594</v>
+        <v>422</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B82" t="s">
         <v>597</v>
       </c>
       <c r="C82" t="s">
+        <v>209</v>
+      </c>
+      <c r="D82" t="s">
+        <v>275</v>
+      </c>
+      <c r="E82" t="s">
+        <v>191</v>
+      </c>
+      <c r="F82" t="s">
         <v>598</v>
       </c>
-      <c r="D82" t="s">
-        <v>461</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="H82" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="F82" t="s">
-        <v>600</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>600</v>
+      </c>
+      <c r="B83" t="s">
+        <v>601</v>
+      </c>
+      <c r="C83" t="s">
         <v>602</v>
       </c>
-      <c r="B83" t="s">
-        <v>597</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>415</v>
+      </c>
+      <c r="E83" t="s">
         <v>603</v>
       </c>
-      <c r="D83" t="s">
-        <v>461</v>
-      </c>
-      <c r="E83" t="s">
-        <v>599</v>
-      </c>
       <c r="F83" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>601</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
+        <v>607</v>
       </c>
       <c r="D84" t="s">
-        <v>203</v>
+        <v>415</v>
       </c>
       <c r="E84" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F84" t="s">
-        <v>240</v>
+        <v>604</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B85" t="s">
-        <v>609</v>
+        <v>238</v>
       </c>
       <c r="C85" t="s">
+        <v>209</v>
+      </c>
+      <c r="D85" t="s">
+        <v>203</v>
+      </c>
+      <c r="E85" t="s">
         <v>610</v>
       </c>
-      <c r="D85" t="s">
-        <v>203</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>240</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="F85" t="s">
-        <v>612</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>612</v>
+      </c>
+      <c r="B86" t="s">
+        <v>613</v>
+      </c>
+      <c r="C86" t="s">
         <v>614</v>
       </c>
-      <c r="B86" t="s">
-        <v>249</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>203</v>
+      </c>
+      <c r="E86" t="s">
         <v>615</v>
       </c>
-      <c r="D86" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>616</v>
-      </c>
-      <c r="F86" t="s">
-        <v>391</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>617</v>
@@ -6221,171 +6230,171 @@
         <v>618</v>
       </c>
       <c r="B87" t="s">
+        <v>249</v>
+      </c>
+      <c r="C87" t="s">
         <v>619</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" t="s">
         <v>620</v>
       </c>
-      <c r="D87" t="s">
-        <v>203</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
+        <v>391</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F87" t="s">
-        <v>622</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>622</v>
+      </c>
+      <c r="B88" t="s">
+        <v>623</v>
+      </c>
+      <c r="C88" t="s">
         <v>624</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
+        <v>203</v>
+      </c>
+      <c r="E88" t="s">
         <v>625</v>
       </c>
-      <c r="C88" t="s">
+      <c r="F88" t="s">
         <v>626</v>
       </c>
-      <c r="D88" t="s">
-        <v>203</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="H88" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="F88" t="s">
-        <v>628</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>628</v>
+      </c>
+      <c r="B89" t="s">
+        <v>629</v>
+      </c>
+      <c r="C89" t="s">
         <v>630</v>
       </c>
-      <c r="B89" t="s">
+      <c r="D89" t="s">
+        <v>203</v>
+      </c>
+      <c r="E89" t="s">
         <v>631</v>
       </c>
-      <c r="C89" t="s">
-        <v>209</v>
-      </c>
-      <c r="D89" t="s">
-        <v>550</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>632</v>
       </c>
-      <c r="F89" t="s">
+      <c r="H89" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>634</v>
+      </c>
+      <c r="B90" t="s">
         <v>635</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" t="s">
+        <v>555</v>
+      </c>
+      <c r="E90" t="s">
         <v>636</v>
       </c>
-      <c r="C90" t="s">
+      <c r="F90" t="s">
         <v>637</v>
       </c>
-      <c r="D90" t="s">
-        <v>203</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="H90" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="F90" t="s">
-        <v>191</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>639</v>
+      </c>
+      <c r="B91" t="s">
         <v>640</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>641</v>
       </c>
-      <c r="C91" t="s">
-        <v>209</v>
-      </c>
       <c r="D91" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E91" t="s">
         <v>642</v>
       </c>
       <c r="F91" t="s">
+        <v>191</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>644</v>
+      </c>
+      <c r="B92" t="s">
         <v>645</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
+        <v>209</v>
+      </c>
+      <c r="D92" t="s">
+        <v>275</v>
+      </c>
+      <c r="E92" t="s">
         <v>646</v>
       </c>
-      <c r="C92" t="s">
+      <c r="F92" t="s">
         <v>647</v>
       </c>
-      <c r="D92" t="s">
-        <v>203</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="H92" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="F92" t="s">
-        <v>649</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B93" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C93" t="s">
-        <v>339</v>
+        <v>651</v>
       </c>
       <c r="D93" t="s">
         <v>203</v>
       </c>
       <c r="E93" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F93" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C94" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="D94" t="s">
         <v>203</v>
@@ -6394,44 +6403,44 @@
         <v>655</v>
       </c>
       <c r="F94" t="s">
+        <v>653</v>
+      </c>
+      <c r="H94" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>657</v>
+      </c>
+      <c r="B95" t="s">
         <v>658</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
+        <v>209</v>
+      </c>
+      <c r="D95" t="s">
+        <v>203</v>
+      </c>
+      <c r="E95" t="s">
         <v>659</v>
       </c>
-      <c r="C95" t="s">
+      <c r="F95" t="s">
         <v>660</v>
       </c>
-      <c r="D95" t="s">
-        <v>203</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="H95" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="F95" t="s">
-        <v>662</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>662</v>
+      </c>
+      <c r="B96" t="s">
+        <v>663</v>
+      </c>
+      <c r="C96" t="s">
         <v>664</v>
-      </c>
-      <c r="B96" t="s">
-        <v>619</v>
-      </c>
-      <c r="C96" t="s">
-        <v>620</v>
       </c>
       <c r="D96" t="s">
         <v>203</v>
@@ -6440,191 +6449,191 @@
         <v>665</v>
       </c>
       <c r="F96" t="s">
-        <v>191</v>
+        <v>666</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B97" t="s">
-        <v>668</v>
+        <v>623</v>
       </c>
       <c r="C97" t="s">
+        <v>624</v>
+      </c>
+      <c r="D97" t="s">
+        <v>203</v>
+      </c>
+      <c r="E97" t="s">
         <v>669</v>
       </c>
-      <c r="D97" t="s">
-        <v>203</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
+        <v>191</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="F97" t="s">
-        <v>671</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>671</v>
+      </c>
+      <c r="B98" t="s">
+        <v>672</v>
+      </c>
+      <c r="C98" t="s">
         <v>673</v>
       </c>
-      <c r="B98" t="s">
+      <c r="D98" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" t="s">
         <v>674</v>
       </c>
-      <c r="C98" t="s">
+      <c r="F98" t="s">
         <v>675</v>
       </c>
-      <c r="D98" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="H98" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="F98" t="s">
-        <v>677</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>677</v>
+      </c>
+      <c r="B99" t="s">
+        <v>678</v>
+      </c>
+      <c r="C99" t="s">
         <v>679</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D99" t="s">
+        <v>203</v>
+      </c>
+      <c r="E99" t="s">
         <v>680</v>
       </c>
-      <c r="C99" t="s">
-        <v>209</v>
-      </c>
-      <c r="D99" t="s">
-        <v>203</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>681</v>
       </c>
-      <c r="F99" t="s">
+      <c r="H99" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>683</v>
+      </c>
+      <c r="B100" t="s">
         <v>684</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
+        <v>209</v>
+      </c>
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" t="s">
         <v>685</v>
       </c>
-      <c r="C100" t="s">
+      <c r="F100" t="s">
         <v>686</v>
       </c>
-      <c r="D100" t="s">
-        <v>203</v>
-      </c>
-      <c r="E100" t="s">
-        <v>204</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="H100" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>688</v>
+      </c>
+      <c r="B101" t="s">
         <v>689</v>
       </c>
-      <c r="B101" t="s">
-        <v>328</v>
-      </c>
       <c r="C101" t="s">
-        <v>209</v>
+        <v>690</v>
       </c>
       <c r="D101" t="s">
         <v>203</v>
       </c>
       <c r="E101" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F101" t="s">
-        <v>329</v>
+        <v>691</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B102" t="s">
-        <v>692</v>
+        <v>328</v>
       </c>
       <c r="C102" t="s">
-        <v>693</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
+        <v>191</v>
+      </c>
+      <c r="F102" t="s">
+        <v>329</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="F102" t="s">
-        <v>677</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>695</v>
+      </c>
+      <c r="B103" t="s">
         <v>696</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>697</v>
       </c>
-      <c r="C103" t="s">
-        <v>280</v>
-      </c>
       <c r="D103" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E103" t="s">
         <v>698</v>
       </c>
       <c r="F103" t="s">
+        <v>681</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>700</v>
+      </c>
+      <c r="B104" t="s">
         <v>701</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>280</v>
+      </c>
+      <c r="D104" t="s">
+        <v>203</v>
+      </c>
+      <c r="E104" t="s">
         <v>702</v>
       </c>
-      <c r="C104" t="s">
-        <v>479</v>
-      </c>
-      <c r="D104" t="s">
-        <v>203</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>703</v>
-      </c>
-      <c r="F104" t="s">
-        <v>217</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>704</v>
@@ -6638,7 +6647,7 @@
         <v>706</v>
       </c>
       <c r="C105" t="s">
-        <v>339</v>
+        <v>484</v>
       </c>
       <c r="D105" t="s">
         <v>203</v>
@@ -6647,159 +6656,159 @@
         <v>707</v>
       </c>
       <c r="F105" t="s">
+        <v>217</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>709</v>
+      </c>
+      <c r="B106" t="s">
         <v>710</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C106" t="s">
+        <v>339</v>
+      </c>
+      <c r="D106" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" t="s">
         <v>711</v>
       </c>
-      <c r="C106" t="s">
+      <c r="F106" t="s">
         <v>712</v>
       </c>
-      <c r="D106" t="s">
-        <v>461</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="H106" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="F106" t="s">
-        <v>714</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>714</v>
+      </c>
+      <c r="B107" t="s">
+        <v>715</v>
+      </c>
+      <c r="C107" t="s">
         <v>716</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
+        <v>415</v>
+      </c>
+      <c r="E107" t="s">
         <v>717</v>
       </c>
-      <c r="C107" t="s">
+      <c r="F107" t="s">
         <v>718</v>
       </c>
-      <c r="D107" t="s">
-        <v>203</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="H107" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="F107" t="s">
-        <v>720</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>720</v>
+      </c>
+      <c r="B108" t="s">
+        <v>721</v>
+      </c>
+      <c r="C108" t="s">
         <v>722</v>
       </c>
-      <c r="B108" t="s">
+      <c r="D108" t="s">
+        <v>203</v>
+      </c>
+      <c r="E108" t="s">
         <v>723</v>
       </c>
-      <c r="C108" t="s">
+      <c r="F108" t="s">
         <v>724</v>
       </c>
-      <c r="D108" t="s">
-        <v>203</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="H108" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="F108" t="s">
-        <v>726</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>726</v>
+      </c>
+      <c r="B109" t="s">
+        <v>727</v>
+      </c>
+      <c r="C109" t="s">
         <v>728</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
+        <v>203</v>
+      </c>
+      <c r="E109" t="s">
         <v>729</v>
       </c>
-      <c r="C109" t="s">
-        <v>367</v>
-      </c>
-      <c r="D109" t="s">
-        <v>461</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>730</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B110" t="s">
-        <v>231</v>
+        <v>733</v>
       </c>
       <c r="C110" t="s">
-        <v>733</v>
+        <v>367</v>
       </c>
       <c r="D110" t="s">
-        <v>550</v>
+        <v>415</v>
       </c>
       <c r="E110" t="s">
         <v>734</v>
       </c>
       <c r="F110" t="s">
-        <v>235</v>
+        <v>735</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B111" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" t="s">
         <v>737</v>
       </c>
-      <c r="C111" t="s">
-        <v>367</v>
-      </c>
       <c r="D111" t="s">
-        <v>203</v>
+        <v>555</v>
       </c>
       <c r="E111" t="s">
         <v>738</v>
       </c>
       <c r="F111" t="s">
+        <v>235</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B112" t="s">
         <v>741</v>
       </c>
       <c r="C112" t="s">
-        <v>470</v>
+        <v>367</v>
       </c>
       <c r="D112" t="s">
         <v>203</v>
@@ -6816,68 +6825,68 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>740</v>
+      </c>
+      <c r="B113" t="s">
         <v>745</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
+        <v>475</v>
+      </c>
+      <c r="D113" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" t="s">
         <v>746</v>
       </c>
-      <c r="C113" t="s">
+      <c r="F113" t="s">
         <v>747</v>
       </c>
-      <c r="D113" t="s">
-        <v>203</v>
-      </c>
-      <c r="E113" t="s">
-        <v>425</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="H113" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>749</v>
+      </c>
+      <c r="B114" t="s">
         <v>750</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>751</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>203</v>
+      </c>
+      <c r="E114" t="s">
+        <v>431</v>
+      </c>
+      <c r="F114" t="s">
         <v>752</v>
       </c>
-      <c r="D114" t="s">
-        <v>275</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="H114" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="F114" t="s">
-        <v>754</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>754</v>
+      </c>
+      <c r="B115" t="s">
+        <v>755</v>
+      </c>
+      <c r="C115" t="s">
         <v>756</v>
       </c>
-      <c r="B115" t="s">
+      <c r="D115" t="s">
+        <v>275</v>
+      </c>
+      <c r="E115" t="s">
         <v>757</v>
       </c>
-      <c r="C115" t="s">
-        <v>323</v>
-      </c>
-      <c r="D115" t="s">
-        <v>203</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>758</v>
-      </c>
-      <c r="F115" t="s">
-        <v>677</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>759</v>
@@ -6891,62 +6900,62 @@
         <v>761</v>
       </c>
       <c r="C116" t="s">
+        <v>323</v>
+      </c>
+      <c r="D116" t="s">
+        <v>203</v>
+      </c>
+      <c r="E116" t="s">
         <v>762</v>
       </c>
-      <c r="D116" t="s">
-        <v>461</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
+        <v>681</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="F116" t="s">
-        <v>600</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>764</v>
+      </c>
+      <c r="B117" t="s">
         <v>765</v>
       </c>
-      <c r="B117" t="s">
-        <v>548</v>
-      </c>
       <c r="C117" t="s">
-        <v>549</v>
+        <v>766</v>
       </c>
       <c r="D117" t="s">
-        <v>550</v>
+        <v>415</v>
       </c>
       <c r="E117" t="s">
-        <v>551</v>
+        <v>767</v>
       </c>
       <c r="F117" t="s">
-        <v>552</v>
+        <v>604</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B118" t="s">
-        <v>768</v>
+        <v>553</v>
       </c>
       <c r="C118" t="s">
-        <v>367</v>
+        <v>554</v>
       </c>
       <c r="D118" t="s">
-        <v>203</v>
+        <v>555</v>
       </c>
       <c r="E118" t="s">
-        <v>769</v>
+        <v>556</v>
       </c>
       <c r="F118" t="s">
-        <v>228</v>
+        <v>557</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>770</v>
@@ -6957,42 +6966,42 @@
         <v>771</v>
       </c>
       <c r="B119" t="s">
-        <v>360</v>
+        <v>772</v>
       </c>
       <c r="C119" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D119" t="s">
         <v>203</v>
       </c>
       <c r="E119" t="s">
-        <v>719</v>
+        <v>773</v>
       </c>
       <c r="F119" t="s">
-        <v>363</v>
+        <v>228</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B120" t="s">
-        <v>774</v>
+        <v>360</v>
       </c>
       <c r="C120" t="s">
-        <v>209</v>
+        <v>361</v>
       </c>
       <c r="D120" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E120" t="s">
-        <v>539</v>
+        <v>723</v>
       </c>
       <c r="F120" t="s">
-        <v>775</v>
+        <v>363</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>776</v>
@@ -7006,177 +7015,177 @@
         <v>778</v>
       </c>
       <c r="C121" t="s">
-        <v>479</v>
+        <v>209</v>
       </c>
       <c r="D121" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E121" t="s">
+        <v>544</v>
+      </c>
+      <c r="F121" t="s">
         <v>779</v>
       </c>
-      <c r="F121" t="s">
+      <c r="H121" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>781</v>
+      </c>
+      <c r="B122" t="s">
         <v>782</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
+        <v>484</v>
+      </c>
+      <c r="D122" t="s">
+        <v>203</v>
+      </c>
+      <c r="E122" t="s">
         <v>783</v>
       </c>
-      <c r="C122" t="s">
+      <c r="F122" t="s">
         <v>784</v>
       </c>
-      <c r="D122" t="s">
-        <v>203</v>
-      </c>
-      <c r="E122" t="s">
-        <v>621</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="H122" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>786</v>
+      </c>
+      <c r="B123" t="s">
         <v>787</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>788</v>
       </c>
-      <c r="C123" t="s">
-        <v>339</v>
-      </c>
       <c r="D123" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="E123" t="s">
-        <v>191</v>
+        <v>625</v>
       </c>
       <c r="F123" t="s">
-        <v>205</v>
+        <v>789</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B124" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C124" t="s">
-        <v>202</v>
+        <v>339</v>
       </c>
       <c r="D124" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="E124" t="s">
-        <v>792</v>
+        <v>191</v>
       </c>
       <c r="F124" t="s">
+        <v>205</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>794</v>
+      </c>
+      <c r="B125" t="s">
         <v>795</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
+        <v>202</v>
+      </c>
+      <c r="D125" t="s">
+        <v>203</v>
+      </c>
+      <c r="E125" t="s">
         <v>796</v>
       </c>
-      <c r="C125" t="s">
-        <v>221</v>
-      </c>
-      <c r="D125" t="s">
-        <v>203</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>797</v>
       </c>
-      <c r="F125" t="s">
+      <c r="H125" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>799</v>
+      </c>
+      <c r="B126" t="s">
         <v>800</v>
       </c>
-      <c r="B126" t="s">
-        <v>394</v>
-      </c>
       <c r="C126" t="s">
-        <v>395</v>
+        <v>221</v>
       </c>
       <c r="D126" t="s">
         <v>203</v>
       </c>
       <c r="E126" t="s">
-        <v>191</v>
+        <v>801</v>
       </c>
       <c r="F126" t="s">
-        <v>396</v>
+        <v>802</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>194</v>
+        <v>804</v>
       </c>
       <c r="B127" t="s">
-        <v>802</v>
+        <v>394</v>
       </c>
       <c r="C127" t="s">
-        <v>803</v>
+        <v>395</v>
       </c>
       <c r="D127" t="s">
         <v>203</v>
       </c>
       <c r="E127" t="s">
-        <v>804</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
+        <v>396</v>
+      </c>
+      <c r="H127" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>194</v>
+      </c>
+      <c r="B128" t="s">
+        <v>806</v>
+      </c>
+      <c r="C128" t="s">
         <v>807</v>
       </c>
-      <c r="B128" t="s">
+      <c r="D128" t="s">
+        <v>203</v>
+      </c>
+      <c r="E128" t="s">
         <v>808</v>
       </c>
-      <c r="C128" t="s">
+      <c r="F128" t="s">
         <v>809</v>
-      </c>
-      <c r="D128" t="s">
-        <v>203</v>
-      </c>
-      <c r="E128" t="s">
-        <v>436</v>
-      </c>
-      <c r="F128" t="s">
-        <v>329</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>810</v>
@@ -7190,16 +7199,16 @@
         <v>812</v>
       </c>
       <c r="C129" t="s">
-        <v>209</v>
+        <v>813</v>
       </c>
       <c r="D129" t="s">
         <v>203</v>
       </c>
       <c r="E129" t="s">
-        <v>813</v>
+        <v>442</v>
       </c>
       <c r="F129" t="s">
-        <v>191</v>
+        <v>329</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>814</v>
@@ -7213,7 +7222,7 @@
         <v>816</v>
       </c>
       <c r="C130" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D130" t="s">
         <v>203</v>
@@ -7222,30 +7231,30 @@
         <v>817</v>
       </c>
       <c r="F130" t="s">
+        <v>191</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>819</v>
+      </c>
+      <c r="B131" t="s">
         <v>820</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
+        <v>221</v>
+      </c>
+      <c r="D131" t="s">
+        <v>203</v>
+      </c>
+      <c r="E131" t="s">
         <v>821</v>
       </c>
-      <c r="C131" t="s">
-        <v>202</v>
-      </c>
-      <c r="D131" t="s">
-        <v>461</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>822</v>
-      </c>
-      <c r="F131" t="s">
-        <v>563</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>823</v>
@@ -7256,134 +7265,134 @@
         <v>824</v>
       </c>
       <c r="B132" t="s">
+        <v>414</v>
+      </c>
+      <c r="C132" t="s">
+        <v>202</v>
+      </c>
+      <c r="D132" t="s">
+        <v>415</v>
+      </c>
+      <c r="E132" t="s">
         <v>825</v>
       </c>
-      <c r="C132" t="s">
+      <c r="F132" t="s">
+        <v>417</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="D132" t="s">
-        <v>203</v>
-      </c>
-      <c r="E132" t="s">
-        <v>827</v>
-      </c>
-      <c r="F132" t="s">
-        <v>391</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>827</v>
+      </c>
+      <c r="B133" t="s">
+        <v>828</v>
+      </c>
+      <c r="C133" t="s">
         <v>829</v>
       </c>
-      <c r="B133" t="s">
+      <c r="D133" t="s">
+        <v>203</v>
+      </c>
+      <c r="E133" t="s">
         <v>830</v>
       </c>
-      <c r="C133" t="s">
-        <v>262</v>
-      </c>
-      <c r="D133" t="s">
-        <v>203</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
+        <v>391</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="F133" t="s">
-        <v>832</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B134" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C134" t="s">
+        <v>262</v>
+      </c>
+      <c r="D134" t="s">
+        <v>203</v>
+      </c>
+      <c r="E134" t="s">
         <v>834</v>
       </c>
-      <c r="D134" t="s">
-        <v>203</v>
-      </c>
-      <c r="E134" t="s">
-        <v>831</v>
-      </c>
       <c r="F134" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B135" t="s">
+        <v>833</v>
+      </c>
+      <c r="C135" t="s">
         <v>837</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>203</v>
+      </c>
+      <c r="E135" t="s">
+        <v>834</v>
+      </c>
+      <c r="F135" t="s">
+        <v>835</v>
+      </c>
+      <c r="H135" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="D135" t="s">
-        <v>203</v>
-      </c>
-      <c r="E135" t="s">
-        <v>839</v>
-      </c>
-      <c r="F135" t="s">
-        <v>840</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>839</v>
+      </c>
+      <c r="B136" t="s">
+        <v>840</v>
+      </c>
+      <c r="C136" t="s">
+        <v>841</v>
+      </c>
+      <c r="D136" t="s">
+        <v>203</v>
+      </c>
+      <c r="E136" t="s">
         <v>842</v>
       </c>
-      <c r="B136" t="s">
+      <c r="F136" t="s">
         <v>843</v>
       </c>
-      <c r="C136" t="s">
+      <c r="H136" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="D136" t="s">
-        <v>461</v>
-      </c>
-      <c r="E136" t="s">
-        <v>845</v>
-      </c>
-      <c r="F136" t="s">
-        <v>846</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>845</v>
+      </c>
+      <c r="B137" t="s">
+        <v>846</v>
+      </c>
+      <c r="C137" t="s">
+        <v>847</v>
+      </c>
+      <c r="D137" t="s">
+        <v>415</v>
+      </c>
+      <c r="E137" t="s">
         <v>848</v>
       </c>
-      <c r="B137" t="s">
+      <c r="F137" t="s">
         <v>849</v>
-      </c>
-      <c r="C137" t="s">
-        <v>209</v>
-      </c>
-      <c r="D137" t="s">
-        <v>203</v>
-      </c>
-      <c r="E137" t="s">
-        <v>719</v>
-      </c>
-      <c r="F137" t="s">
-        <v>329</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>850</v>
@@ -7403,47 +7412,47 @@
         <v>203</v>
       </c>
       <c r="E138" t="s">
+        <v>723</v>
+      </c>
+      <c r="F138" t="s">
+        <v>329</v>
+      </c>
+      <c r="H138" s="2" t="s">
         <v>853</v>
-      </c>
-      <c r="F138" t="s">
-        <v>854</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>854</v>
+      </c>
+      <c r="B139" t="s">
+        <v>855</v>
+      </c>
+      <c r="C139" t="s">
+        <v>209</v>
+      </c>
+      <c r="D139" t="s">
+        <v>203</v>
+      </c>
+      <c r="E139" t="s">
         <v>856</v>
       </c>
-      <c r="B139" t="s">
+      <c r="F139" t="s">
         <v>857</v>
       </c>
-      <c r="C139" t="s">
+      <c r="H139" s="2" t="s">
         <v>858</v>
-      </c>
-      <c r="D139" t="s">
-        <v>203</v>
-      </c>
-      <c r="E139" t="s">
-        <v>859</v>
-      </c>
-      <c r="F139" t="s">
-        <v>329</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>859</v>
+      </c>
+      <c r="B140" t="s">
+        <v>860</v>
+      </c>
+      <c r="C140" t="s">
         <v>861</v>
-      </c>
-      <c r="B140" t="s">
-        <v>609</v>
-      </c>
-      <c r="C140" t="s">
-        <v>610</v>
       </c>
       <c r="D140" t="s">
         <v>203</v>
@@ -7452,7 +7461,7 @@
         <v>862</v>
       </c>
       <c r="F140" t="s">
-        <v>633</v>
+        <v>329</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>863</v>
@@ -7460,22 +7469,22 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B141" t="s">
-        <v>864</v>
+        <v>613</v>
       </c>
       <c r="C141" t="s">
+        <v>614</v>
+      </c>
+      <c r="D141" t="s">
+        <v>203</v>
+      </c>
+      <c r="E141" t="s">
         <v>865</v>
       </c>
-      <c r="D141" t="s">
-        <v>203</v>
-      </c>
-      <c r="E141" t="s">
-        <v>191</v>
-      </c>
       <c r="F141" t="s">
-        <v>391</v>
+        <v>637</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>866</v>
@@ -7483,79 +7492,79 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B142" t="s">
         <v>867</v>
       </c>
       <c r="C142" t="s">
-        <v>209</v>
+        <v>868</v>
       </c>
       <c r="D142" t="s">
         <v>203</v>
       </c>
       <c r="E142" t="s">
-        <v>868</v>
+        <v>191</v>
       </c>
       <c r="F142" t="s">
+        <v>391</v>
+      </c>
+      <c r="H142" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>864</v>
+      </c>
+      <c r="B143" t="s">
+        <v>870</v>
+      </c>
+      <c r="C143" t="s">
+        <v>209</v>
+      </c>
+      <c r="D143" t="s">
+        <v>203</v>
+      </c>
+      <c r="E143" t="s">
         <v>871</v>
       </c>
-      <c r="B143" t="s">
+      <c r="F143" t="s">
         <v>872</v>
       </c>
-      <c r="C143" t="s">
-        <v>858</v>
-      </c>
-      <c r="D143" t="s">
-        <v>203</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="H143" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="F143" t="s">
-        <v>874</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>874</v>
+      </c>
+      <c r="B144" t="s">
+        <v>875</v>
+      </c>
+      <c r="C144" t="s">
+        <v>861</v>
+      </c>
+      <c r="D144" t="s">
+        <v>203</v>
+      </c>
+      <c r="E144" t="s">
         <v>876</v>
       </c>
-      <c r="B144" t="s">
-        <v>872</v>
-      </c>
-      <c r="C144" t="s">
-        <v>367</v>
-      </c>
-      <c r="D144" t="s">
-        <v>203</v>
-      </c>
-      <c r="E144" t="s">
-        <v>873</v>
-      </c>
       <c r="F144" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B145" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C145" t="s">
         <v>367</v>
@@ -7564,79 +7573,79 @@
         <v>203</v>
       </c>
       <c r="E145" t="s">
+        <v>876</v>
+      </c>
+      <c r="F145" t="s">
+        <v>877</v>
+      </c>
+      <c r="H145" s="2" t="s">
         <v>880</v>
-      </c>
-      <c r="F145" t="s">
-        <v>881</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>881</v>
+      </c>
+      <c r="B146" t="s">
+        <v>882</v>
+      </c>
+      <c r="C146" t="s">
+        <v>367</v>
+      </c>
+      <c r="D146" t="s">
+        <v>203</v>
+      </c>
+      <c r="E146" t="s">
         <v>883</v>
       </c>
-      <c r="B146" t="s">
+      <c r="F146" t="s">
         <v>884</v>
       </c>
-      <c r="C146" t="s">
+      <c r="H146" s="2" t="s">
         <v>885</v>
-      </c>
-      <c r="D146" t="s">
-        <v>203</v>
-      </c>
-      <c r="E146" t="s">
-        <v>886</v>
-      </c>
-      <c r="F146" t="s">
-        <v>887</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>886</v>
+      </c>
+      <c r="B147" t="s">
+        <v>887</v>
+      </c>
+      <c r="C147" t="s">
+        <v>888</v>
+      </c>
+      <c r="D147" t="s">
+        <v>203</v>
+      </c>
+      <c r="E147" t="s">
         <v>889</v>
       </c>
-      <c r="B147" t="s">
+      <c r="F147" t="s">
         <v>890</v>
       </c>
-      <c r="C147" t="s">
+      <c r="H147" s="2" t="s">
         <v>891</v>
-      </c>
-      <c r="D147" t="s">
-        <v>203</v>
-      </c>
-      <c r="E147" t="s">
-        <v>892</v>
-      </c>
-      <c r="F147" t="s">
-        <v>191</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>892</v>
+      </c>
+      <c r="B148" t="s">
+        <v>893</v>
+      </c>
+      <c r="C148" t="s">
         <v>894</v>
       </c>
-      <c r="B148" t="s">
-        <v>857</v>
-      </c>
-      <c r="C148" t="s">
-        <v>858</v>
-      </c>
       <c r="D148" t="s">
-        <v>550</v>
+        <v>203</v>
       </c>
       <c r="E148" t="s">
         <v>895</v>
       </c>
       <c r="F148" t="s">
-        <v>329</v>
+        <v>191</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>896</v>
@@ -7647,180 +7656,180 @@
         <v>897</v>
       </c>
       <c r="B149" t="s">
-        <v>619</v>
+        <v>860</v>
       </c>
       <c r="C149" t="s">
+        <v>861</v>
+      </c>
+      <c r="D149" t="s">
+        <v>555</v>
+      </c>
+      <c r="E149" t="s">
         <v>898</v>
       </c>
-      <c r="D149" t="s">
-        <v>550</v>
-      </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
+        <v>329</v>
+      </c>
+      <c r="H149" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="F149" t="s">
-        <v>191</v>
-      </c>
-      <c r="H149" s="2" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>900</v>
+      </c>
+      <c r="B150" t="s">
+        <v>623</v>
+      </c>
+      <c r="C150" t="s">
         <v>901</v>
       </c>
-      <c r="B150" t="s">
-        <v>399</v>
-      </c>
-      <c r="C150" t="s">
-        <v>400</v>
-      </c>
       <c r="D150" t="s">
-        <v>233</v>
+        <v>555</v>
       </c>
       <c r="E150" t="s">
-        <v>191</v>
+        <v>902</v>
       </c>
       <c r="F150" t="s">
         <v>191</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B151" t="s">
-        <v>904</v>
+        <v>399</v>
       </c>
       <c r="C151" t="s">
-        <v>905</v>
+        <v>400</v>
       </c>
       <c r="D151" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="E151" t="s">
-        <v>906</v>
+        <v>191</v>
       </c>
       <c r="F151" t="s">
         <v>191</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>906</v>
+      </c>
+      <c r="B152" t="s">
+        <v>907</v>
+      </c>
+      <c r="C152" t="s">
         <v>908</v>
       </c>
-      <c r="B152" t="s">
+      <c r="D152" t="s">
+        <v>203</v>
+      </c>
+      <c r="E152" t="s">
         <v>909</v>
       </c>
-      <c r="C152" t="s">
-        <v>226</v>
-      </c>
-      <c r="D152" t="s">
-        <v>203</v>
-      </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
+        <v>191</v>
+      </c>
+      <c r="H152" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="F152" t="s">
-        <v>911</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>911</v>
+      </c>
+      <c r="B153" t="s">
+        <v>912</v>
+      </c>
+      <c r="C153" t="s">
+        <v>226</v>
+      </c>
+      <c r="D153" t="s">
+        <v>203</v>
+      </c>
+      <c r="E153" t="s">
         <v>913</v>
       </c>
-      <c r="B153" t="s">
+      <c r="F153" t="s">
         <v>914</v>
       </c>
-      <c r="C153" t="s">
-        <v>367</v>
-      </c>
-      <c r="D153" t="s">
-        <v>203</v>
-      </c>
-      <c r="E153" t="s">
+      <c r="H153" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="F153" t="s">
-        <v>191</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>916</v>
+      </c>
+      <c r="B154" t="s">
         <v>917</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
+        <v>367</v>
+      </c>
+      <c r="D154" t="s">
+        <v>203</v>
+      </c>
+      <c r="E154" t="s">
         <v>918</v>
       </c>
-      <c r="C154" t="s">
+      <c r="F154" t="s">
+        <v>191</v>
+      </c>
+      <c r="H154" s="2" t="s">
         <v>919</v>
-      </c>
-      <c r="D154" t="s">
-        <v>203</v>
-      </c>
-      <c r="E154" t="s">
-        <v>920</v>
-      </c>
-      <c r="F154" t="s">
-        <v>205</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>920</v>
+      </c>
+      <c r="B155" t="s">
+        <v>921</v>
+      </c>
+      <c r="C155" t="s">
         <v>922</v>
       </c>
-      <c r="B155" t="s">
+      <c r="D155" t="s">
+        <v>203</v>
+      </c>
+      <c r="E155" t="s">
         <v>923</v>
       </c>
-      <c r="C155" t="s">
+      <c r="F155" t="s">
+        <v>205</v>
+      </c>
+      <c r="H155" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="D155" t="s">
-        <v>203</v>
-      </c>
-      <c r="E155" t="s">
-        <v>925</v>
-      </c>
-      <c r="F155" t="s">
-        <v>926</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>925</v>
+      </c>
+      <c r="B156" t="s">
+        <v>926</v>
+      </c>
+      <c r="C156" t="s">
+        <v>927</v>
+      </c>
+      <c r="D156" t="s">
+        <v>203</v>
+      </c>
+      <c r="E156" t="s">
         <v>928</v>
       </c>
-      <c r="B156" t="s">
-        <v>872</v>
-      </c>
-      <c r="C156" t="s">
-        <v>339</v>
-      </c>
-      <c r="D156" t="s">
-        <v>203</v>
-      </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>929</v>
-      </c>
-      <c r="F156" t="s">
-        <v>874</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>930</v>
@@ -7828,68 +7837,68 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B157" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C157" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="D157" t="s">
         <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="F157" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B158" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C158" t="s">
-        <v>858</v>
+        <v>367</v>
       </c>
       <c r="D158" t="s">
         <v>203</v>
       </c>
       <c r="E158" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="F158" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B159" t="s">
-        <v>399</v>
+        <v>875</v>
       </c>
       <c r="C159" t="s">
-        <v>400</v>
+        <v>861</v>
       </c>
       <c r="D159" t="s">
         <v>203</v>
       </c>
       <c r="E159" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F159" t="s">
-        <v>402</v>
+        <v>877</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>935</v>
@@ -7900,88 +7909,88 @@
         <v>936</v>
       </c>
       <c r="B160" t="s">
+        <v>399</v>
+      </c>
+      <c r="C160" t="s">
+        <v>400</v>
+      </c>
+      <c r="D160" t="s">
+        <v>203</v>
+      </c>
+      <c r="E160" t="s">
         <v>937</v>
       </c>
-      <c r="C160" t="s">
+      <c r="F160" t="s">
+        <v>402</v>
+      </c>
+      <c r="H160" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="D160" t="s">
-        <v>203</v>
-      </c>
-      <c r="E160" t="s">
-        <v>591</v>
-      </c>
-      <c r="F160" t="s">
-        <v>939</v>
-      </c>
-      <c r="H160" s="2" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>939</v>
+      </c>
+      <c r="B161" t="s">
+        <v>940</v>
+      </c>
+      <c r="C161" t="s">
         <v>941</v>
       </c>
-      <c r="B161" t="s">
+      <c r="D161" t="s">
+        <v>203</v>
+      </c>
+      <c r="E161" t="s">
+        <v>595</v>
+      </c>
+      <c r="F161" t="s">
         <v>942</v>
       </c>
-      <c r="C161" t="s">
+      <c r="H161" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="D161" t="s">
-        <v>461</v>
-      </c>
-      <c r="E161" t="s">
-        <v>944</v>
-      </c>
-      <c r="F161" t="s">
-        <v>945</v>
-      </c>
-      <c r="H161" s="2" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>944</v>
+      </c>
+      <c r="B162" t="s">
+        <v>945</v>
+      </c>
+      <c r="C162" t="s">
+        <v>946</v>
+      </c>
+      <c r="D162" t="s">
+        <v>415</v>
+      </c>
+      <c r="E162" t="s">
         <v>947</v>
       </c>
-      <c r="B162" t="s">
+      <c r="F162" t="s">
         <v>948</v>
       </c>
-      <c r="C162" t="s">
+      <c r="H162" s="2" t="s">
         <v>949</v>
-      </c>
-      <c r="D162" t="s">
-        <v>203</v>
-      </c>
-      <c r="E162" t="s">
-        <v>950</v>
-      </c>
-      <c r="F162" t="s">
-        <v>951</v>
-      </c>
-      <c r="H162" s="2" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>950</v>
+      </c>
+      <c r="B163" t="s">
+        <v>951</v>
+      </c>
+      <c r="C163" t="s">
+        <v>952</v>
+      </c>
+      <c r="D163" t="s">
+        <v>203</v>
+      </c>
+      <c r="E163" t="s">
         <v>953</v>
       </c>
-      <c r="B163" t="s">
-        <v>231</v>
-      </c>
-      <c r="C163" t="s">
-        <v>232</v>
-      </c>
-      <c r="D163" t="s">
-        <v>233</v>
-      </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>954</v>
-      </c>
-      <c r="F163" t="s">
-        <v>235</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>955</v>
@@ -7992,22 +8001,45 @@
         <v>956</v>
       </c>
       <c r="B164" t="s">
+        <v>231</v>
+      </c>
+      <c r="C164" t="s">
+        <v>232</v>
+      </c>
+      <c r="D164" t="s">
+        <v>233</v>
+      </c>
+      <c r="E164" t="s">
         <v>957</v>
       </c>
-      <c r="C164" t="s">
+      <c r="F164" t="s">
+        <v>235</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>959</v>
+      </c>
+      <c r="B165" t="s">
+        <v>960</v>
+      </c>
+      <c r="C165" t="s">
         <v>226</v>
       </c>
-      <c r="D164" t="s">
-        <v>203</v>
-      </c>
-      <c r="E164" t="s">
-        <v>958</v>
-      </c>
-      <c r="F164" t="s">
-        <v>959</v>
-      </c>
-      <c r="H164" s="2" t="s">
-        <v>960</v>
+      <c r="D165" t="s">
+        <v>203</v>
+      </c>
+      <c r="E165" t="s">
+        <v>961</v>
+      </c>
+      <c r="F165" t="s">
+        <v>962</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -8176,6 +8208,7 @@
     <hyperlink ref="H162" r:id="rId161"/>
     <hyperlink ref="H163" r:id="rId162"/>
     <hyperlink ref="H164" r:id="rId163"/>
+    <hyperlink ref="H165" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
